--- a/data/trending_integrated_20260911_12.xlsx
+++ b/data/trending_integrated_20260911_12.xlsx
@@ -571,20 +571,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+27.36%</t>
+          <t>+29.94%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.22</v>
       </c>
       <c r="E2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F2" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G2" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="H2" t="n">
         <v>2.39</v>
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>12610</v>
+        <v>12360</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>12800</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>16060</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>12690</v>
       </c>
       <c r="N2" t="n">
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>207017000000</v>
+        <v>207160304445</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>30550</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="R2" t="n">
         <v>-71000</v>
@@ -626,12 +626,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>젠슨 황의 AI 다음 시장으로 사이버 보안 지목에 따른 엑스게이트의 급등 기대. 양자보안 관련성 언급.</t>
+          <t>Nvidia CEO 젠슨 황의 사이버 보안 시장 전망 언급에 따른 급등, 양자 보안 관련 기대감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2580</v>
+        <v>15620</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+21.41%</t>
+          <t>+29.20%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.07000000000000001</v>
+        <v>3.11</v>
       </c>
       <c r="E3" t="n">
-        <v>69</v>
+        <v>335</v>
       </c>
       <c r="F3" t="n">
-        <v>52</v>
+        <v>205</v>
       </c>
       <c r="G3" t="n">
-        <v>93</v>
+        <v>808</v>
       </c>
       <c r="H3" t="n">
-        <v>3.83</v>
+        <v>3.14</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,91 +687,91 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2125</v>
+        <v>12090</v>
       </c>
       <c r="K3" t="n">
-        <v>2230</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2692</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2170</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.76</v>
+        <v>0.03</v>
       </c>
       <c r="O3" t="n">
-        <v>88193948291</v>
+        <v>179760000000</v>
       </c>
       <c r="P3" t="n">
-        <v>4810</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-359000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>젠슨 황의 사이버보안 섹터 지목과 함께 양자컴퓨터 보조금 지원 소식 언급. 드림시큐리티의 대장주로서의 부각 및 상승 신호.</t>
+          <t>중동 전쟁 우려 및 유가 급등에 따른 흥구석유의 3연상 기대감. 국제유가 변동성 관련 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['젠슨황', '사이버보안', '양자컴퓨터']</t>
+          <t>['국제유가', '중동 전쟁', '전쟁 테마주']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8020</v>
+        <v>2555</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+19.70%</t>
+          <t>+20.24%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.79</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="F4" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G4" t="n">
-        <v>229</v>
+        <v>97</v>
       </c>
       <c r="H4" t="n">
-        <v>2.15</v>
+        <v>3.83</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,60 +779,60 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>6700</v>
+        <v>2125</v>
       </c>
       <c r="K4" t="n">
-        <v>6530</v>
+        <v>2230</v>
       </c>
       <c r="L4" t="n">
-        <v>8370</v>
+        <v>2692</v>
       </c>
       <c r="M4" t="n">
-        <v>6430</v>
+        <v>2170</v>
       </c>
       <c r="N4" t="n">
-        <v>2.94</v>
+        <v>3.76</v>
       </c>
       <c r="O4" t="n">
-        <v>132808124035</v>
+        <v>89821468451</v>
       </c>
       <c r="P4" t="n">
-        <v>16200</v>
+        <v>4810</v>
       </c>
       <c r="Q4" t="n">
-        <v>1206</v>
+        <v>1400</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-1884000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>광통신 및 위성 네트워크 사업과의 연관성, 대장주로서의 기대감. 상한가 기록 가능성 언급.</t>
+          <t>젠슨 황의 사이버보안 섹터 지목과 함께 양자컴퓨터 보조금 지원 소식 언급. 드림시큐리티의 대장주로서의 부각 및 상승 신호.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['광통신', '위성네트워크', '대장주']</t>
+          <t>['젠슨황', '사이버보안', '양자컴퓨터']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>138500</v>
+        <v>138800</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+19.09%</t>
+          <t>+19.97%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.26</v>
       </c>
       <c r="E5" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F5" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G5" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H5" t="n">
         <v>4.32</v>
@@ -871,28 +871,28 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>116300</v>
+        <v>115700</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>112100</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>147500</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>112000</v>
       </c>
       <c r="N5" t="n">
         <v>4.58</v>
       </c>
       <c r="O5" t="n">
-        <v>427067000000</v>
+        <v>430874131600</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>196800</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>27750</v>
       </c>
       <c r="R5" t="n">
         <v>52000</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>애플 관련 호재에 따른 주가 상승 기대감. 거래량 부진 및 손바뀜 현상 언급.</t>
+          <t>애플 관련 호재로 인한 급등세, 거래량 감소와 함께 일회성 호재 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['애플', '거래량', '손바뀜']</t>
+          <t>['애플', '급등', '거래량']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8300</v>
+        <v>7840</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+11.86%</t>
+          <t>+19.33%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.12</v>
+        <v>-0.79</v>
       </c>
       <c r="E6" t="n">
-        <v>170</v>
+        <v>93</v>
       </c>
       <c r="F6" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="G6" t="n">
-        <v>731</v>
+        <v>253</v>
       </c>
       <c r="H6" t="n">
-        <v>1.29</v>
+        <v>2.15</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>7420</v>
+        <v>6570</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -975,10 +975,10 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.17</v>
+        <v>2.94</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>140837000000</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -987,27 +987,27 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>141000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>WCLC 세계폐암학회에서의 센딥 파텔 교수 데이터 발표에 따른 주가 대폭등 예고. 기술 수출 기대감.</t>
+          <t>광통신 및 위성 네트워크 관련주로 부각, 대장주로서의 기대감과 함께 단기 급등 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['폐암학회', '기술수출', '임상']</t>
+          <t>['광통신', '위성네트워크', '대장주']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1928</v>
+        <v>1934</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+9.55%</t>
+          <t>+9.89%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.32</v>
       </c>
       <c r="E7" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F7" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G7" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H7" t="n">
         <v>2.44</v>
@@ -1070,7 +1070,7 @@
         <v>2.12</v>
       </c>
       <c r="O7" t="n">
-        <v>38483000000</v>
+        <v>38910000000</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1079,14 +1079,14 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-591000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>홍해 사태로 인한 유가 상승 및 전쟁 테마주로서의 기대감. 장금상선 관련 정보 언급.</t>
+          <t>홍해 지정학적 리스크와 유가 상승에 따른 전쟁 테마주 부각. 장금상선과의 연관성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['전쟁테마', '유가상승', '홍해']</t>
+          <t>['홍해', '유가', '전쟁테마주']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,83 +1115,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15580</v>
+        <v>7680</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+7.37%</t>
+          <t>+8.17%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3.11</v>
+        <v>0.1</v>
       </c>
       <c r="E8" t="n">
-        <v>332</v>
+        <v>109</v>
       </c>
       <c r="F8" t="n">
-        <v>204</v>
+        <v>57</v>
       </c>
       <c r="G8" t="n">
-        <v>801</v>
+        <v>348</v>
       </c>
       <c r="H8" t="n">
-        <v>3.14</v>
+        <v>11.72</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14510</v>
+        <v>7100</v>
       </c>
       <c r="K8" t="n">
-        <v>17010</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>17310</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>15290</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03</v>
+        <v>11.62</v>
       </c>
       <c r="O8" t="n">
-        <v>176645534235</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>36200</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>8920</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-359000</v>
+        <v>43000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>중동 전쟁 우려 및 유가 급등에 따른 흥구석유의 3연상 기대감. 국제유가 변동성 관련 언급.</t>
+          <t>공매도 및 대차 물량 관찰 속 8000원대 돌파 시도 및 주가 변동성 관측.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['국제유가', '중동 전쟁', '전쟁 테마주']</t>
+          <t>['공매도', '대차', '변동성']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,99 +1200,99 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>253000</v>
+        <v>9940</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>+7.11%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.96</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>205</v>
+        <v>67</v>
       </c>
       <c r="F9" t="n">
-        <v>103</v>
+        <v>40</v>
       </c>
       <c r="G9" t="n">
-        <v>697</v>
+        <v>290</v>
       </c>
       <c r="H9" t="n">
-        <v>7.58</v>
+        <v>4.49</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>250500</v>
+        <v>9280</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>10030</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>10880</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>9800</v>
       </c>
       <c r="N9" t="n">
-        <v>8.539999999999999</v>
+        <v>4.42</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>20298273100</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>15640</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5470</v>
       </c>
       <c r="R9" t="n">
-        <v>-298000</v>
+        <v>-88000</v>
       </c>
       <c r="S9" t="n">
-        <v>-18000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>기관의 꾸준한 매수에도 불구하고 주가 하락. 공매도에 대한 불만 및 주가 방어 요구.</t>
+          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['공매도', '기관매수', '주가방어']</t>
+          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>064550</t>
         </is>
       </c>
     </row>
@@ -1303,18 +1303,18 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53300</v>
+        <v>53500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.44</v>
       </c>
       <c r="E10" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F10" t="n">
         <v>38</v>
@@ -1346,7 +1346,7 @@
         <v>3.36</v>
       </c>
       <c r="O10" t="n">
-        <v>83830000000</v>
+        <v>84536000000</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>90000</v>
+        <v>19500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.06</v>
+        <v>0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>192</v>
+        <v>127</v>
       </c>
       <c r="F11" t="n">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="G11" t="n">
-        <v>770</v>
+        <v>424</v>
       </c>
       <c r="H11" t="n">
-        <v>23.59</v>
+        <v>10.65</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>89900</v>
+        <v>19450</v>
       </c>
       <c r="K11" t="n">
-        <v>88700</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>91000</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>23.65</v>
+        <v>10.64</v>
       </c>
       <c r="O11" t="n">
-        <v>116504993250</v>
+        <v>82022000000</v>
       </c>
       <c r="P11" t="n">
-        <v>139200</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-264000</v>
+        <v>-233000</v>
       </c>
       <c r="S11" t="n">
-        <v>26000</v>
+        <v>-16000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 투자 협상 마무리 및 중동 에너지 공급망 이슈에 따른 두산에너빌리티의 수혜 기대. 수주 잔고 언급.</t>
+          <t>대차 해지를 통한 공매도 세력 대응 촉구. 목표가 상향 및 대규모 투자 유치 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['원전', '에너지 공급망', '수주 잔고']</t>
+          <t>['대차해지', '공매도', '목표가 상향']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1853000</v>
+        <v>416000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.12</v>
+        <v>0.2</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>85</v>
       </c>
       <c r="F12" t="n">
-        <v>464</v>
+        <v>44</v>
       </c>
       <c r="G12" t="n">
-        <v>1270</v>
+        <v>214</v>
       </c>
       <c r="H12" t="n">
-        <v>50.55</v>
+        <v>38.02</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1856000</v>
+        <v>415500</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>407000</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>418000</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>404000</v>
       </c>
       <c r="N12" t="n">
-        <v>50.67</v>
+        <v>37.82</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>44456786500</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>822000</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>283000</v>
       </c>
       <c r="R12" t="n">
-        <v>-249000</v>
+        <v>13000</v>
       </c>
       <c r="S12" t="n">
-        <v>-102000</v>
+        <v>1000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>SK하이닉스 소폭 하락에도 불구하고 일부 투자자들은 반등을 기대하며 추가 매수를 고려하고 있습니다. 다만, 외국인 및 기관의 대규모 매도와 관련된 우려도 존재합니다.</t>
+          <t>로봇 부품 사업 확장 및 글로벌 수주 기대감, 유럽 중국차 관세 이슈 반사이익 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['하락', '매수', '반등']</t>
+          <t>['로봇', '수주', '미래차']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>012330</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>415500</v>
+        <v>50400</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="E13" t="n">
-        <v>85</v>
+        <v>138</v>
       </c>
       <c r="F13" t="n">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="G13" t="n">
-        <v>212</v>
+        <v>527</v>
       </c>
       <c r="H13" t="n">
-        <v>38.02</v>
+        <v>38.78</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>417500</v>
+        <v>50800</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1619,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>37.82</v>
+        <v>38.69</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1631,27 +1631,27 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>-134000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>로봇 사업 확장 및 신기술 공개로 인한 수주 기대감. 유럽 중국차 관세 관련 호재 및 저평가 논의.</t>
+          <t>약 4.7조원 규모의 대규모 수주 공시로 인한 긍정적 시장 반응 및 상승 추세 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['로봇 사업', '수주', '관세']</t>
+          <t>['수주', '공시', '추세']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19600</v>
+        <v>29550</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.76%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.01</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>130</v>
+        <v>49</v>
       </c>
       <c r="F14" t="n">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="G14" t="n">
-        <v>425</v>
+        <v>132</v>
       </c>
       <c r="H14" t="n">
-        <v>10.65</v>
+        <v>25.55</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,91 +1699,91 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>19750</v>
+        <v>29800</v>
       </c>
       <c r="K14" t="n">
-        <v>19500</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>19840</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>19060</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>10.64</v>
+        <v>24.99</v>
       </c>
       <c r="O14" t="n">
-        <v>79722616815</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-233000</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-16000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>대차 해지를 통한 공매도 세력 대응 촉구. 목표가 상향 및 대규모 투자 유치 기대.</t>
+          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '목표가 상향']</t>
+          <t>['유럽 자금', '환율', '유가']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>50400</v>
+        <v>14760</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-1.86%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>136</v>
+        <v>67</v>
       </c>
       <c r="F15" t="n">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="G15" t="n">
-        <v>516</v>
+        <v>236</v>
       </c>
       <c r="H15" t="n">
-        <v>38.78</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,91 +1791,91 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>50800</v>
+        <v>15040</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>14550</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>15260</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>14350</v>
       </c>
       <c r="N15" t="n">
-        <v>38.69</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>17465396705</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>19380</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>약 4.7조원 규모의 대규모 수주 공시 확인. 사우디 및 베트남 관련 복합 호재 기대감 형성.</t>
+          <t>금호건설, 호남 반도체 부지 100만평 추가 확보 검토 및 삼성전자 신축 공장 수주 소식. 친환경 및 폐기물 처리 사업 관련 성장성 기대.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['수주', '공시', '호재']</t>
+          <t>['반도체 부지', '신축 공장 수주', '친환경']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>29550</v>
+        <v>89900</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="E16" t="n">
-        <v>48</v>
+        <v>195</v>
       </c>
       <c r="F16" t="n">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="G16" t="n">
-        <v>134</v>
+        <v>775</v>
       </c>
       <c r="H16" t="n">
-        <v>25.55</v>
+        <v>23.59</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>29800</v>
+        <v>91700</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1895,7 +1895,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>24.99</v>
+        <v>23.65</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -1907,36 +1907,36 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>265000</v>
+        <v>-264000</v>
       </c>
       <c r="S16" t="n">
-        <v>-69000</v>
+        <v>26000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
+          <t>미국 투자 협상 마무리 및 중동 에너지 공급망 이슈에 따른 두산에너빌리티의 수혜 기대. 수주 잔고 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['유럽 자금', '환율', '유가']</t>
+          <t>['원전', '에너지 공급망', '수주 잔고']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8810</v>
+        <v>8790</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>-2.01%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.03</v>
       </c>
       <c r="E17" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F17" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G17" t="n">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H17" t="n">
         <v>27.19</v>
@@ -1990,7 +1990,7 @@
         <v>27.16</v>
       </c>
       <c r="O17" t="n">
-        <v>14187749710</v>
+        <v>14774121395</v>
       </c>
       <c r="P17" t="n">
         <v>17950</v>
@@ -2035,83 +2035,83 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14180</v>
+        <v>193000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>-2.28%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F18" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G18" t="n">
-        <v>474</v>
+        <v>129</v>
       </c>
       <c r="H18" t="n">
-        <v>5.98</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>14600</v>
+        <v>197500</v>
       </c>
       <c r="K18" t="n">
-        <v>14800</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>14950</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>14020</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>6.09</v>
+        <v>75.92</v>
       </c>
       <c r="O18" t="n">
-        <v>86037023735</v>
+        <v>376902000000</v>
       </c>
       <c r="P18" t="n">
-        <v>30200</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3540</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>-852000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-123000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>자포리 원전 이슈와 관련된 주가 급등 기대감. 모건 스탠리의 대량 매수세 언급.</t>
+          <t>기관 및 외국인 매도세 지속, 주가 하락에 대한 불안감과 특별 배당 기대감 혼재.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['원전', '자포리', '모건스탠리']</t>
+          <t>['기관매도', '주가하락', '특별배당']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,90 +2120,90 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7400</v>
+        <v>14180</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.65%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="E19" t="n">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="F19" t="n">
         <v>57</v>
       </c>
       <c r="G19" t="n">
-        <v>339</v>
+        <v>490</v>
       </c>
       <c r="H19" t="n">
-        <v>11.72</v>
+        <v>5.98</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>7680</v>
+        <v>14600</v>
       </c>
       <c r="K19" t="n">
-        <v>7540</v>
+        <v>14800</v>
       </c>
       <c r="L19" t="n">
-        <v>7660</v>
+        <v>14950</v>
       </c>
       <c r="M19" t="n">
-        <v>7390</v>
+        <v>14020</v>
       </c>
       <c r="N19" t="n">
-        <v>11.62</v>
+        <v>6.09</v>
       </c>
       <c r="O19" t="n">
-        <v>8206344775</v>
+        <v>87131994145</v>
       </c>
       <c r="P19" t="n">
-        <v>8850</v>
+        <v>30200</v>
       </c>
       <c r="Q19" t="n">
-        <v>4220</v>
+        <v>3540</v>
       </c>
       <c r="R19" t="n">
-        <v>43000</v>
+        <v>-371000</v>
       </c>
       <c r="S19" t="n">
-        <v>-2000</v>
+        <v>-69000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>기사 기반 호재 및 기관 매수세 유입 가능성 언급, 전고점 돌파 기대.</t>
+          <t>자포리 원전 관련 소식과 함께 주가 변동성 확대, 모건 증권의 대량 매도 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['호재', '기관 매수', '전고점']</t>
+          <t>['원전', '자포리', '모건증권']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,130 +2212,130 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15040</v>
+        <v>14220</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.84%</t>
+          <t>-3.53%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
       <c r="E20" t="n">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="F20" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G20" t="n">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>15640</v>
+        <v>14740</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>14050</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>14560</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>14030</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>47213161205</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1272</v>
       </c>
       <c r="R20" t="n">
-        <v>22000</v>
+        <v>-128000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>금호건설, 호남 반도체 부지 100만평 추가 확보 검토 및 삼성전자 신축 공장 수주 소식. 친환경 및 폐기물 처리 사업 관련 성장성 기대.</t>
+          <t>광통신 사업 및 미국 시장 진출 기대감. 외국인 매수세 유입에 따른 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['반도체 부지', '신축 공장 수주', '친환경']</t>
+          <t>['광통신', '미국진출', '외국인']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>257500</v>
+        <v>1782000</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-4.45%</t>
+          <t>-3.83%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.1</v>
+        <v>-0.12</v>
       </c>
       <c r="E21" t="n">
         <v>800</v>
       </c>
       <c r="F21" t="n">
-        <v>509</v>
+        <v>465</v>
       </c>
       <c r="G21" t="n">
-        <v>1574</v>
+        <v>1325</v>
       </c>
       <c r="H21" t="n">
-        <v>46.71</v>
+        <v>50.55</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,38 +2343,38 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>269500</v>
+        <v>1853000</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1773000</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1795000</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1768000</v>
       </c>
       <c r="N21" t="n">
-        <v>46.81</v>
+        <v>50.67</v>
       </c>
       <c r="O21" t="n">
-        <v>1909980000000</v>
+        <v>2515066784000</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2987000</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>305500</v>
       </c>
       <c r="R21" t="n">
-        <v>-1232000</v>
+        <v>-249000</v>
       </c>
       <c r="S21" t="n">
-        <v>-646000</v>
+        <v>-102000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>반도체 수출 역대 최대에도 불구하고 주가 하락에 대한 불만. 정치적 요인 언급.</t>
+          <t>하락장 속에서 외인 및 기관 매도세 관찰, 금리 변동성 속 주가 등락 전망.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,11 +2383,11 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['반도체 수출', '주가 하락', '정치적 요인']</t>
+          <t>['하락', '외국인', '기관']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,90 +2396,90 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14240</v>
+        <v>257500</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-4.81%</t>
+          <t>-4.28%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.39</v>
+        <v>-0.1</v>
       </c>
       <c r="E22" t="n">
-        <v>87</v>
+        <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>51</v>
+        <v>513</v>
       </c>
       <c r="G22" t="n">
-        <v>220</v>
+        <v>1575</v>
       </c>
       <c r="H22" t="n">
-        <v>2.5</v>
+        <v>46.71</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>14960</v>
+        <v>269000</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>258000</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>261000</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>257000</v>
       </c>
       <c r="N22" t="n">
-        <v>2.89</v>
+        <v>46.81</v>
       </c>
       <c r="O22" t="n">
-        <v>46454000000</v>
+        <v>1973860474750</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>374500</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>72100</v>
       </c>
       <c r="R22" t="n">
-        <v>-128000</v>
+        <v>-1232000</v>
       </c>
       <c r="S22" t="n">
-        <v>-6000</v>
+        <v>-646000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>광통신 사업 및 미국 시장 진출 기대감. 외국인 매수세 유입에 따른 주가 상승 전망.</t>
+          <t>수출 부진 우려와 반도체 주가 하락세 지속, 기대에 못 미치는 주가 흐름에 대한 불만.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['광통신', '미국진출', '외국인']</t>
+          <t>['수출', '반도체', '주가하락']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,77 +2488,77 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>193100</v>
+        <v>12370</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-4.88%</t>
+          <t>-5.07%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="E23" t="n">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="F23" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G23" t="n">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="H23" t="n">
-        <v>75.98999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>203000</v>
+        <v>13030</v>
       </c>
       <c r="K23" t="n">
-        <v>195000</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>195600</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>191000</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>75.92</v>
+        <v>0.14</v>
       </c>
       <c r="O23" t="n">
-        <v>371725891100</v>
+        <v>38625000000</v>
       </c>
       <c r="P23" t="n">
-        <v>243500</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>58600</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>-852000</v>
+        <v>-69000</v>
       </c>
       <c r="S23" t="n">
-        <v>-123000</v>
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>미국 증시 하락 및 기관/외인 매도세로 주가 하락 압력을 받으며, 배당금 대비 주가 하락에 대한 불만이 나타남.</t>
+          <t>원전 테마주로서의 삼미금속 언급. 한전기술 등 타 원전주들의 급등 속 상대적 부진 및 거래량 부족에 대한 지적.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,11 +2567,11 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['우선주', '기관 매도', '미국 증시']</t>
+          <t>['원전', '테마주', '거래량']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,38 +2580,38 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9280</v>
+        <v>7680</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-5.31%</t>
+          <t>-7.47%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="E24" t="n">
-        <v>66</v>
+        <v>171</v>
       </c>
       <c r="F24" t="n">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="G24" t="n">
-        <v>286</v>
+        <v>736</v>
       </c>
       <c r="H24" t="n">
-        <v>4.49</v>
+        <v>1.29</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2619,152 +2619,152 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>9800</v>
+        <v>8300</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>8400</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>8700</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>7540</v>
       </c>
       <c r="N24" t="n">
-        <v>4.42</v>
+        <v>1.17</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>16483184880</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>21500</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="R24" t="n">
-        <v>-88000</v>
+        <v>-12000</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
+          <t>WCLC 세계폐암학회에서의 센딥 파텔 교수 데이터 발표에 따른 주가 대폭등 예고. 기술 수출 기대감.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
+          <t>['폐암학회', '기술수출', '임상']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>12160</v>
+        <v>232500</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-6.68%</t>
+          <t>-8.10%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.8</v>
+        <v>-0.96</v>
       </c>
       <c r="E25" t="n">
-        <v>65</v>
+        <v>213</v>
       </c>
       <c r="F25" t="n">
-        <v>40</v>
+        <v>106</v>
       </c>
       <c r="G25" t="n">
-        <v>61</v>
+        <v>731</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9399999999999999</v>
+        <v>7.58</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>13030</v>
+        <v>253000</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>241000</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>241000</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>231000</v>
       </c>
       <c r="N25" t="n">
-        <v>0.14</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>37994000000</v>
+        <v>166055972750</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>426000</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>86100</v>
       </c>
       <c r="R25" t="n">
-        <v>-69000</v>
+        <v>-298000</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>-18000</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>원전 테마주로서의 삼미금속 언급. 한전기술 등 타 원전주들의 급등 속 상대적 부진 및 거래량 부족에 대한 지적.</t>
+          <t>HBM 관련주로 언급되나 주가 하락세 지속, 공매도 및 기관 매도세에 대한 우려.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['원전', '테마주', '거래량']</t>
+          <t>['HBM', '공매도', '주가하락']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
         <v>34</v>
       </c>
       <c r="G26" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H26" t="n">
         <v>0.73</v>
@@ -2818,7 +2818,7 @@
         <v>1.54</v>
       </c>
       <c r="O26" t="n">
-        <v>39183000000</v>
+        <v>39732000000</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2867,24 +2867,24 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27250</v>
+        <v>26700</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-10.07%</t>
+          <t>-11.88%</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>-0.01</v>
       </c>
       <c r="E27" t="n">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="F27" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G27" t="n">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="H27" t="n">
         <v>0.32</v>
@@ -2910,7 +2910,7 @@
         <v>0.33</v>
       </c>
       <c r="O27" t="n">
-        <v>295184000000</v>
+        <v>299128000000</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2926,16 +2926,16 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>급등 가능성에 대한 기대감 표출. 전반적인 시장 상황 및 투자 심리 언급.</t>
+          <t>기대 이상의 주가 흐름, 외인 매수세 유입 가능성과 함께 지수 하락장 속 상대적 강세.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['급등', '투자심리', '시장상황']</t>
+          <t>['주가흐름', '외인매수', '지수하락']</t>
         </is>
       </c>
       <c r="X27" t="n">

--- a/data/trending_integrated_20260911_12.xlsx
+++ b/data/trending_integrated_20260911_12.xlsx
@@ -578,13 +578,13 @@
         <v>-0.22</v>
       </c>
       <c r="E2" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G2" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="H2" t="n">
         <v>2.39</v>
@@ -610,7 +610,7 @@
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>207160304445</v>
+        <v>207229426685</v>
       </c>
       <c r="P2" t="n">
         <v>30550</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Nvidia CEO 젠슨 황의 사이버 보안 시장 전망 언급에 따른 급등, 양자 보안 관련 기대감.</t>
+          <t>AI 다음 시장으로 사이버 보안 주목. 젠슨 황 발언 및 관련 뉴스 인용, 양자보안 기술 강조.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['사이버보안', 'AI', '젠슨황']</t>
+          <t>['사이버보안', '젠슨황', '양자보안']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15620</v>
+        <v>15610</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+29.20%</t>
+          <t>+29.11%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>3.11</v>
       </c>
       <c r="E3" t="n">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="F3" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G3" t="n">
-        <v>808</v>
+        <v>839</v>
       </c>
       <c r="H3" t="n">
         <v>3.14</v>
@@ -702,7 +702,7 @@
         <v>0.03</v>
       </c>
       <c r="O3" t="n">
-        <v>179760000000</v>
+        <v>182542000000</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>중동 전쟁 우려 및 유가 급등에 따른 흥구석유의 3연상 기대감. 국제유가 변동성 관련 언급.</t>
+          <t>국제 유가 급등 및 중동 지정학적 리스크 부각. 3연상 및 15,000원 지지선 돌파 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['국제유가', '중동 전쟁', '전쟁 테마주']</t>
+          <t>['국제유가', '지정학적리스크', '3연상']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2555</v>
+        <v>2550</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+20.24%</t>
+          <t>+19.44%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F4" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G4" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="H4" t="n">
         <v>3.83</v>
@@ -779,28 +779,28 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2125</v>
+        <v>2135</v>
       </c>
       <c r="K4" t="n">
-        <v>2230</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2692</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2170</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>3.76</v>
       </c>
       <c r="O4" t="n">
-        <v>89821468451</v>
+        <v>90445000000</v>
       </c>
       <c r="P4" t="n">
-        <v>4810</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>-1884000</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>138800</v>
+        <v>137700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+19.97%</t>
+          <t>+18.40%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.26</v>
       </c>
       <c r="E5" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F5" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G5" t="n">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="H5" t="n">
         <v>4.32</v>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>115700</v>
+        <v>116300</v>
       </c>
       <c r="K5" t="n">
-        <v>112100</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>147500</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>112000</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>4.58</v>
       </c>
       <c r="O5" t="n">
-        <v>430874131600</v>
+        <v>433675000000</v>
       </c>
       <c r="P5" t="n">
-        <v>196800</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>27750</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>52000</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>96000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>애플 관련 호재로 인한 급등세, 거래량 감소와 함께 일회성 호재 가능성 언급.</t>
+          <t>거래량 부진 속 애플 관련 호재 가능성 언급. 단기 급등 기대와 경계 혼재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['애플', '급등', '거래량']</t>
+          <t>['거래량', '애플', '단기급등']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7840</v>
+        <v>7800</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+19.33%</t>
+          <t>+16.42%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.79</v>
       </c>
       <c r="E6" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F6" t="n">
         <v>65</v>
       </c>
       <c r="G6" t="n">
-        <v>253</v>
+        <v>287</v>
       </c>
       <c r="H6" t="n">
         <v>2.15</v>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6570</v>
+        <v>6700</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>6530</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>8370</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>6430</v>
       </c>
       <c r="N6" t="n">
         <v>2.94</v>
       </c>
       <c r="O6" t="n">
-        <v>140837000000</v>
+        <v>143900698080</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1206</v>
       </c>
       <c r="R6" t="n">
-        <v>141000</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>광통신 및 위성 네트워크 관련주로 부각, 대장주로서의 기대감과 함께 단기 급등 가능성 언급.</t>
+          <t>통신 및 위성네트워크 사업 관련 기대감. 공매도 감소 언급 및 단기 급등 가능성 제시.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['광통신', '위성네트워크', '대장주']</t>
+          <t>['통신', '위성네트워크', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,39 +1023,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1934</v>
+        <v>8300</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+9.89%</t>
+          <t>+11.86%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.32</v>
+        <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>111</v>
+        <v>176</v>
       </c>
       <c r="F7" t="n">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="G7" t="n">
-        <v>188</v>
+        <v>756</v>
       </c>
       <c r="H7" t="n">
-        <v>2.44</v>
+        <v>1.29</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1760</v>
+        <v>7420</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>1.17</v>
       </c>
       <c r="O7" t="n">
-        <v>38910000000</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1079,27 +1079,27 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-591000</v>
+        <v>-12000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>홍해 지정학적 리스크와 유가 상승에 따른 전쟁 테마주 부각. 장금상선과의 연관성 언급.</t>
+          <t>WCLC 세계폐암학회에서의 센딥 파텔 교수 데이터 발표에 따른 주가 대폭등 예고. 기술 수출 기대감.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['홍해', '유가', '전쟁테마주']</t>
+          <t>['폐암학회', '기술수출', '임상']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7680</v>
+        <v>1931</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+8.17%</t>
+          <t>+9.72%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.1</v>
+        <v>0.32</v>
       </c>
       <c r="E8" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F8" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G8" t="n">
-        <v>348</v>
+        <v>186</v>
       </c>
       <c r="H8" t="n">
-        <v>11.72</v>
+        <v>2.44</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7100</v>
+        <v>1760</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1159,10 +1159,10 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>11.62</v>
+        <v>2.12</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>39323000000</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1171,23 +1171,23 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>43000</v>
+        <v>-591000</v>
       </c>
       <c r="S8" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>공매도 및 대차 물량 관찰 속 8000원대 돌파 시도 및 주가 변동성 관측.</t>
+          <t>홍해 지정학적 리스크 및 유가 상승에 따른 전쟁 테마주 분류. 장금상선 지분율 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['공매도', '대차', '변동성']</t>
+          <t>['전쟁테마', '유가상승', '장금상선']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,86 +1200,86 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9940</v>
+        <v>7680</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+7.11%</t>
+          <t>+8.17%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="E9" t="n">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="F9" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="G9" t="n">
-        <v>290</v>
+        <v>353</v>
       </c>
       <c r="H9" t="n">
-        <v>4.49</v>
+        <v>11.72</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>9280</v>
+        <v>7100</v>
       </c>
       <c r="K9" t="n">
-        <v>10030</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>10880</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>9800</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.42</v>
+        <v>11.62</v>
       </c>
       <c r="O9" t="n">
-        <v>20298273100</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>15640</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5470</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>-88000</v>
+        <v>43000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
+          <t>내일 주가 상승에 대한 기대감과 함께 기관 매수세 및 굿뉴스 언급이 있으나, 주가 상승 저해 요인 및 공매도 관련 내용으로 상쇄되어 구체적 근거는 미흡.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
+          <t>['대차', '공매도', '주포']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,43 +1287,43 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53500</v>
+        <v>416500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+0.56%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.44</v>
+        <v>0.2</v>
       </c>
       <c r="E10" t="n">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="F10" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G10" t="n">
-        <v>126</v>
+        <v>216</v>
       </c>
       <c r="H10" t="n">
-        <v>2.92</v>
+        <v>38.02</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,47 +1331,47 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>53200</v>
+        <v>415500</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>407000</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>418000</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>404000</v>
       </c>
       <c r="N10" t="n">
-        <v>3.36</v>
+        <v>37.82</v>
       </c>
       <c r="O10" t="n">
-        <v>84536000000</v>
+        <v>45603972750</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>822000</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>283000</v>
       </c>
       <c r="R10" t="n">
-        <v>116000</v>
+        <v>13000</v>
       </c>
       <c r="S10" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
+          <t>로봇 부품 사업 확장 및 글로벌 수주 기대감, 유럽 중국차 관세 이슈 반사이익 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['태양광', '고유가', '신호가']</t>
+          <t>['로봇', '수주', '미래차']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,43 +1379,43 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>012330</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19500</v>
+        <v>53200</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.01</v>
+        <v>-0.44</v>
       </c>
       <c r="E11" t="n">
-        <v>127</v>
+        <v>65</v>
       </c>
       <c r="F11" t="n">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="G11" t="n">
-        <v>424</v>
+        <v>128</v>
       </c>
       <c r="H11" t="n">
-        <v>10.65</v>
+        <v>2.92</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>19450</v>
+        <v>53200</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1435,10 +1435,10 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>10.64</v>
+        <v>3.36</v>
       </c>
       <c r="O11" t="n">
-        <v>82022000000</v>
+        <v>85949000000</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1447,67 +1447,67 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-233000</v>
+        <v>116000</v>
       </c>
       <c r="S11" t="n">
-        <v>-16000</v>
+        <v>10000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>대차 해지를 통한 공매도 세력 대응 촉구. 목표가 상향 및 대규모 투자 유치 기대.</t>
+          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '목표가 상향']</t>
+          <t>['태양광', '고유가', '신호가']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>475150</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>416000</v>
+        <v>89900</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.2</v>
+        <v>-0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="F12" t="n">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="G12" t="n">
-        <v>214</v>
+        <v>784</v>
       </c>
       <c r="H12" t="n">
-        <v>38.02</v>
+        <v>23.59</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>415500</v>
+        <v>89900</v>
       </c>
       <c r="K12" t="n">
-        <v>407000</v>
+        <v>88700</v>
       </c>
       <c r="L12" t="n">
-        <v>418000</v>
+        <v>91000</v>
       </c>
       <c r="M12" t="n">
-        <v>404000</v>
+        <v>88000</v>
       </c>
       <c r="N12" t="n">
-        <v>37.82</v>
+        <v>23.65</v>
       </c>
       <c r="O12" t="n">
-        <v>44456786500</v>
+        <v>122559679800</v>
       </c>
       <c r="P12" t="n">
-        <v>822000</v>
+        <v>139200</v>
       </c>
       <c r="Q12" t="n">
-        <v>283000</v>
+        <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>13000</v>
+        <v>-264000</v>
       </c>
       <c r="S12" t="n">
-        <v>1000</v>
+        <v>26000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>로봇 부품 사업 확장 및 글로벌 수주 기대감, 유럽 중국차 관세 이슈 반사이익 전망.</t>
+          <t>미국 투자 협상 마무리 및 중동 에너지 공급망 이슈에 따른 두산에너빌리티의 수혜 기대. 수주 잔고 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['로봇', '수주', '미래차']</t>
+          <t>['원전', '에너지 공급망', '수주 잔고']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>50400</v>
+        <v>1853000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.09</v>
+        <v>-0.12</v>
       </c>
       <c r="E13" t="n">
-        <v>138</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>81</v>
+        <v>459</v>
       </c>
       <c r="G13" t="n">
-        <v>527</v>
+        <v>1342</v>
       </c>
       <c r="H13" t="n">
-        <v>38.78</v>
+        <v>50.55</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>50800</v>
+        <v>1856000</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1619,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>38.69</v>
+        <v>50.67</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1631,27 +1631,27 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-134000</v>
+        <v>-249000</v>
       </c>
       <c r="S13" t="n">
-        <v>2000</v>
+        <v>-102000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>약 4.7조원 규모의 대규모 수주 공시로 인한 긍정적 시장 반응 및 상승 추세 기대.</t>
+          <t>종목 하락 속에서 일부 긍정적 기대와 함께 개인 투자자 매수세 언급이 있으나, 구체적인 호재나 하락 원인 분석 등 객관적 근거는 부족.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['수주', '공시', '추세']</t>
+          <t>['개인투자자', '금리', '박스권']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29550</v>
+        <v>50400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="E14" t="n">
-        <v>49</v>
+        <v>138</v>
       </c>
       <c r="F14" t="n">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="G14" t="n">
-        <v>132</v>
+        <v>534</v>
       </c>
       <c r="H14" t="n">
-        <v>25.55</v>
+        <v>38.78</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>29800</v>
+        <v>50800</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1711,7 +1711,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>24.99</v>
+        <v>38.69</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1723,67 +1723,67 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>-134000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
+          <t>약 4.7조원 규모의 대규모 수주 공시로 인한 긍정적 시장 반응 및 상승 추세 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['유럽 자금', '환율', '유가']</t>
+          <t>['수주', '공시', '추세']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14760</v>
+        <v>29550</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.86%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G15" t="n">
-        <v>236</v>
+        <v>137</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>25.55</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>15040</v>
+        <v>29800</v>
       </c>
       <c r="K15" t="n">
-        <v>14550</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>15260</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>14350</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>24.99</v>
       </c>
       <c r="O15" t="n">
-        <v>17465396705</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>19380</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>22000</v>
+        <v>265000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-69000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>금호건설, 호남 반도체 부지 100만평 추가 확보 검토 및 삼성전자 신축 공장 수주 소식. 친환경 및 폐기물 처리 사업 관련 성장성 기대.</t>
+          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['반도체 부지', '신축 공장 수주', '친환경']</t>
+          <t>['유럽 자금', '환율', '유가']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>89900</v>
+        <v>19550</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>-1.01%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.06</v>
+        <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>195</v>
+        <v>128</v>
       </c>
       <c r="F16" t="n">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="G16" t="n">
-        <v>775</v>
+        <v>443</v>
       </c>
       <c r="H16" t="n">
-        <v>23.59</v>
+        <v>10.65</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>91700</v>
+        <v>19750</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>19500</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>19840</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>19060</v>
       </c>
       <c r="N16" t="n">
-        <v>23.65</v>
+        <v>10.64</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>83905239500</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>40350</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3320</v>
       </c>
       <c r="R16" t="n">
-        <v>-264000</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>26000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 투자 협상 마무리 및 중동 에너지 공급망 이슈에 따른 두산에너빌리티의 수혜 기대. 수주 잔고 언급.</t>
+          <t>대차해지 및 공매도 관련 언급 다수. NH 투자증권 목표가 상향 뉴스 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['원전', '에너지 공급망', '수주 잔고']</t>
+          <t>['대차해지', '공매도', '목표가상향']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,130 +1936,130 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8790</v>
+        <v>14160</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.01%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.03</v>
+        <v>-0.11</v>
       </c>
       <c r="E17" t="n">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="F17" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="G17" t="n">
-        <v>228</v>
+        <v>498</v>
       </c>
       <c r="H17" t="n">
-        <v>27.19</v>
+        <v>5.98</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>8970</v>
+        <v>14320</v>
       </c>
       <c r="K17" t="n">
-        <v>8780</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>8880</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>8680</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>27.16</v>
+        <v>6.09</v>
       </c>
       <c r="O17" t="n">
-        <v>14774121395</v>
+        <v>88263000000</v>
       </c>
       <c r="P17" t="n">
-        <v>17950</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>8120</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>-100000</v>
+        <v>-371000</v>
       </c>
       <c r="S17" t="n">
-        <v>-78000</v>
+        <v>-69000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 상승에 대한 강한 불만과 함께 회사의 실적 부진 및 저평가에 대한 부정적인 인식이 지배적임.</t>
+          <t>원자력 발전 섹터 관련 긍정적 전망. 모건 스탠리 매수세 및 120일선 지지 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['저평가', '실적 부진', '금리 인상']</t>
+          <t>['원전', '모건스탠리', '120일선']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>193000</v>
+        <v>8820</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.28%</t>
+          <t>-1.45%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F18" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G18" t="n">
-        <v>129</v>
+        <v>236</v>
       </c>
       <c r="H18" t="n">
-        <v>75.98999999999999</v>
+        <v>27.19</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>197500</v>
+        <v>8950</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2079,10 +2079,10 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>75.92</v>
+        <v>27.16</v>
       </c>
       <c r="O18" t="n">
-        <v>376902000000</v>
+        <v>15012000000</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -2091,14 +2091,14 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-852000</v>
+        <v>-100000</v>
       </c>
       <c r="S18" t="n">
-        <v>-123000</v>
+        <v>-78000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>기관 및 외국인 매도세 지속, 주가 하락에 대한 불안감과 특별 배당 기대감 혼재.</t>
+          <t>경영 성과 및 주가 하락에 대한 강한 불만 표출. 목표 주가 하향 전망.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['기관매도', '주가하락', '특별배당']</t>
+          <t>['경영성과', '주가하락', '목표주가']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,99 +2120,99 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14180</v>
+        <v>14770</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="F19" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="G19" t="n">
-        <v>490</v>
+        <v>243</v>
       </c>
       <c r="H19" t="n">
-        <v>5.98</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>14600</v>
+        <v>15040</v>
       </c>
       <c r="K19" t="n">
-        <v>14800</v>
+        <v>14550</v>
       </c>
       <c r="L19" t="n">
-        <v>14950</v>
+        <v>15260</v>
       </c>
       <c r="M19" t="n">
-        <v>14020</v>
+        <v>14350</v>
       </c>
       <c r="N19" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>87131994145</v>
+        <v>17766360735</v>
       </c>
       <c r="P19" t="n">
-        <v>30200</v>
+        <v>19380</v>
       </c>
       <c r="Q19" t="n">
-        <v>3540</v>
+        <v>3200</v>
       </c>
       <c r="R19" t="n">
-        <v>-371000</v>
+        <v>22000</v>
       </c>
       <c r="S19" t="n">
-        <v>-69000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>자포리 원전 관련 소식과 함께 주가 변동성 확대, 모건 증권의 대량 매도 언급.</t>
+          <t>금호건설, 호남 반도체 부지 100만평 추가 확보 검토 및 삼성전자 신축 공장 수주 소식. 친환경 및 폐기물 처리 사업 관련 성장성 기대.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['원전', '자포리', '모건증권']</t>
+          <t>['반도체 부지', '신축 공장 수주', '친환경']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14220</v>
+        <v>14180</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.53%</t>
+          <t>-3.80%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.39</v>
       </c>
       <c r="E20" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F20" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G20" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="H20" t="n">
         <v>2.5</v>
@@ -2266,7 +2266,7 @@
         <v>2.89</v>
       </c>
       <c r="O20" t="n">
-        <v>47213161205</v>
+        <v>50640476760</v>
       </c>
       <c r="P20" t="n">
         <v>31500</v>
@@ -2311,31 +2311,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1782000</v>
+        <v>257250</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.83%</t>
+          <t>-4.37%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="E21" t="n">
         <v>800</v>
       </c>
       <c r="F21" t="n">
-        <v>465</v>
+        <v>512</v>
       </c>
       <c r="G21" t="n">
-        <v>1325</v>
+        <v>1585</v>
       </c>
       <c r="H21" t="n">
-        <v>50.55</v>
+        <v>46.71</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,38 +2343,38 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>1853000</v>
+        <v>269000</v>
       </c>
       <c r="K21" t="n">
-        <v>1773000</v>
+        <v>258000</v>
       </c>
       <c r="L21" t="n">
-        <v>1795000</v>
+        <v>261000</v>
       </c>
       <c r="M21" t="n">
-        <v>1768000</v>
+        <v>257000</v>
       </c>
       <c r="N21" t="n">
-        <v>50.67</v>
+        <v>46.81</v>
       </c>
       <c r="O21" t="n">
-        <v>2515066784000</v>
+        <v>2011543820250</v>
       </c>
       <c r="P21" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q21" t="n">
-        <v>305500</v>
+        <v>72100</v>
       </c>
       <c r="R21" t="n">
-        <v>-249000</v>
+        <v>-1232000</v>
       </c>
       <c r="S21" t="n">
-        <v>-102000</v>
+        <v>-646000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>하락장 속에서 외인 및 기관 매도세 관찰, 금리 변동성 속 주가 등락 전망.</t>
+          <t>반도체 수출 호조에도 불구하고 주가 부진. 정치적 이슈와 엮이며 개인 투자자 불만 토로.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,11 +2383,11 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['하락', '외국인', '기관']</t>
+          <t>['반도체수출', '주가부진', '정치이슈']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>257500</v>
+        <v>192700</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-4.28%</t>
+          <t>-5.07%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>800</v>
+        <v>82</v>
       </c>
       <c r="F22" t="n">
-        <v>513</v>
+        <v>57</v>
       </c>
       <c r="G22" t="n">
-        <v>1575</v>
+        <v>130</v>
       </c>
       <c r="H22" t="n">
-        <v>46.71</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,51 +2435,51 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>269000</v>
+        <v>203000</v>
       </c>
       <c r="K22" t="n">
-        <v>258000</v>
+        <v>195000</v>
       </c>
       <c r="L22" t="n">
-        <v>261000</v>
+        <v>195600</v>
       </c>
       <c r="M22" t="n">
-        <v>257000</v>
+        <v>191000</v>
       </c>
       <c r="N22" t="n">
-        <v>46.81</v>
+        <v>75.92</v>
       </c>
       <c r="O22" t="n">
-        <v>1973860474750</v>
+        <v>382125511400</v>
       </c>
       <c r="P22" t="n">
-        <v>374500</v>
+        <v>243500</v>
       </c>
       <c r="Q22" t="n">
-        <v>72100</v>
+        <v>58600</v>
       </c>
       <c r="R22" t="n">
-        <v>-1232000</v>
+        <v>-852000</v>
       </c>
       <c r="S22" t="n">
-        <v>-646000</v>
+        <v>-123000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>수출 부진 우려와 반도체 주가 하락세 지속, 기대에 못 미치는 주가 흐름에 대한 불만.</t>
+          <t>기관 및 외국인 매도세 지속, 주가 하락에 대한 불안감과 특별 배당 기대감 혼재.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['수출', '반도체', '주가하락']</t>
+          <t>['기관매도', '주가하락', '특별배당']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12370</v>
+        <v>12360</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-5.07%</t>
+          <t>-5.14%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.8</v>
       </c>
       <c r="E23" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F23" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G23" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H23" t="n">
         <v>0.9399999999999999</v>
@@ -2542,7 +2542,7 @@
         <v>0.14</v>
       </c>
       <c r="O23" t="n">
-        <v>38625000000</v>
+        <v>40566000000</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2587,31 +2587,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7680</v>
+        <v>9280</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-7.47%</t>
+          <t>-5.31%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>171</v>
+        <v>67</v>
       </c>
       <c r="F24" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G24" t="n">
-        <v>736</v>
+        <v>296</v>
       </c>
       <c r="H24" t="n">
-        <v>1.29</v>
+        <v>4.49</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2619,60 +2619,60 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>8300</v>
+        <v>9800</v>
       </c>
       <c r="K24" t="n">
-        <v>8400</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>8700</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>7540</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.17</v>
+        <v>4.42</v>
       </c>
       <c r="O24" t="n">
-        <v>16483184880</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>21500</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>-12000</v>
+        <v>-88000</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>WCLC 세계폐암학회에서의 센딥 파텔 교수 데이터 발표에 따른 주가 대폭등 예고. 기술 수출 기대감.</t>
+          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['폐암학회', '기술수출', '임상']</t>
+          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>064550</t>
         </is>
       </c>
     </row>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>232500</v>
+        <v>233000</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-8.10%</t>
+          <t>-7.91%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.96</v>
       </c>
       <c r="E25" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="F25" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G25" t="n">
-        <v>731</v>
+        <v>744</v>
       </c>
       <c r="H25" t="n">
         <v>7.58</v>
@@ -2726,7 +2726,7 @@
         <v>8.539999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>166055972750</v>
+        <v>167391586000</v>
       </c>
       <c r="P25" t="n">
         <v>426000</v>
@@ -2742,16 +2742,16 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>HBM 관련주로 언급되나 주가 하락세 지속, 공매도 및 기관 매도세에 대한 우려.</t>
+          <t>9월 TC본더 수출 데이터 관련 언급과 공매도 관련 내용이 있으나, 주가 방어 및 회사 차원의 소각/무증 발표 요구 등 감정적이고 구체적 근거가 부족한 내용이 혼재.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['HBM', '공매도', '주가하락']</t>
+          <t>['TC본더', '공매도', '소각']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3535</v>
+        <v>3555</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-8.54%</t>
+          <t>-8.02%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>-0.8100000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F26" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G26" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H26" t="n">
         <v>0.73</v>
@@ -2818,7 +2818,7 @@
         <v>1.54</v>
       </c>
       <c r="O26" t="n">
-        <v>39732000000</v>
+        <v>40318000000</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2827,7 +2827,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>64000</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -2867,24 +2867,24 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26700</v>
+        <v>26800</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-11.88%</t>
+          <t>-11.55%</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>-0.01</v>
       </c>
       <c r="E27" t="n">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="F27" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G27" t="n">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="H27" t="n">
         <v>0.32</v>
@@ -2910,7 +2910,7 @@
         <v>0.33</v>
       </c>
       <c r="O27" t="n">
-        <v>299128000000</v>
+        <v>303142000000</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2926,16 +2926,16 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>기대 이상의 주가 흐름, 외인 매수세 유입 가능성과 함께 지수 하락장 속 상대적 강세.</t>
+          <t>급등주로서의 기대감과 변동성에 대한 언급. 투자자들의 심리적 동요 관찰.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['주가흐름', '외인매수', '지수하락']</t>
+          <t>['급등주', '변동성', '투자심리']</t>
         </is>
       </c>
       <c r="X27" t="n">

--- a/data/trending_integrated_20260911_12.xlsx
+++ b/data/trending_integrated_20260911_12.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16060</v>
+        <v>15680</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+29.94%</t>
+          <t>+29.69%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.22</v>
+        <v>3.11</v>
       </c>
       <c r="E2" t="n">
-        <v>132</v>
+        <v>349</v>
       </c>
       <c r="F2" t="n">
-        <v>90</v>
+        <v>213</v>
       </c>
       <c r="G2" t="n">
-        <v>129</v>
+        <v>845</v>
       </c>
       <c r="H2" t="n">
-        <v>2.39</v>
+        <v>3.14</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>12360</v>
+        <v>12090</v>
       </c>
       <c r="K2" t="n">
-        <v>12800</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>16060</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>12690</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2.61</v>
+        <v>0.03</v>
       </c>
       <c r="O2" t="n">
-        <v>207229426685</v>
+        <v>184686000000</v>
       </c>
       <c r="P2" t="n">
-        <v>30550</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>6100</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-71000</v>
+        <v>-359000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 다음 시장으로 사이버 보안 주목. 젠슨 황 발언 및 관련 뉴스 인용, 양자보안 기술 강조.</t>
+          <t>국제 유가 급등 및 중동 지정학적 리스크 부각. 3연상 및 15,000원 지지선 돌파 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['사이버보안', '젠슨황', '양자보안']</t>
+          <t>['국제유가', '지정학적리스크', '3연상']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15610</v>
+        <v>16060</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+29.11%</t>
+          <t>+27.36%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.11</v>
+        <v>-0.22</v>
       </c>
       <c r="E3" t="n">
-        <v>341</v>
+        <v>133</v>
       </c>
       <c r="F3" t="n">
-        <v>208</v>
+        <v>91</v>
       </c>
       <c r="G3" t="n">
-        <v>839</v>
+        <v>130</v>
       </c>
       <c r="H3" t="n">
-        <v>3.14</v>
+        <v>2.39</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>12090</v>
+        <v>12610</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -699,10 +699,10 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03</v>
+        <v>2.61</v>
       </c>
       <c r="O3" t="n">
-        <v>182542000000</v>
+        <v>207310000000</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -711,27 +711,27 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>-359000</v>
+        <v>-71000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>국제 유가 급등 및 중동 지정학적 리스크 부각. 3연상 및 15,000원 지지선 돌파 기대.</t>
+          <t>AI 다음 시장으로 사이버 보안 주목. 젠슨 황 발언 및 관련 뉴스 인용, 양자보안 기술 강조.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['국제유가', '지정학적리스크', '3연상']</t>
+          <t>['사이버보안', '젠슨황', '양자보안']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2550</v>
+        <v>2555</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+19.44%</t>
+          <t>+20.24%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G4" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H4" t="n">
         <v>3.83</v>
@@ -779,28 +779,28 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2135</v>
+        <v>2125</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2230</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2692</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2170</v>
       </c>
       <c r="N4" t="n">
         <v>3.76</v>
       </c>
       <c r="O4" t="n">
-        <v>90445000000</v>
+        <v>92680046820</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4810</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="R4" t="n">
         <v>-1884000</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>젠슨 황의 사이버보안 섹터 지목과 함께 양자컴퓨터 보조금 지원 소식 언급. 드림시큐리티의 대장주로서의 부각 및 상승 신호.</t>
+          <t>양자컴퓨터 및 사이버 보안 테마 연계 기대감 속 변동성 확대. 외국인 및 기관 매도세 관찰.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['젠슨황', '사이버보안', '양자컴퓨터']</t>
+          <t>['양자컴퓨터', '사이버보안', '외국인매도']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,7 +827,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>137700</v>
+        <v>137600</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+18.40%</t>
+          <t>+18.93%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.26</v>
       </c>
       <c r="E5" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="F5" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G5" t="n">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H5" t="n">
         <v>4.32</v>
@@ -871,34 +871,34 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>116300</v>
+        <v>115700</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>112100</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>147500</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>112000</v>
       </c>
       <c r="N5" t="n">
         <v>4.58</v>
       </c>
       <c r="O5" t="n">
-        <v>433675000000</v>
+        <v>436463437500</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>196800</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>27750</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>52000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>96000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7800</v>
+        <v>7720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+16.42%</t>
+          <t>+15.22%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.79</v>
       </c>
       <c r="E6" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G6" t="n">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="H6" t="n">
         <v>2.15</v>
@@ -978,7 +978,7 @@
         <v>2.94</v>
       </c>
       <c r="O6" t="n">
-        <v>143900698080</v>
+        <v>146656276545</v>
       </c>
       <c r="P6" t="n">
         <v>16200</v>
@@ -987,7 +987,7 @@
         <v>1206</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>141000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1038,13 +1038,13 @@
         <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F7" t="n">
         <v>81</v>
       </c>
       <c r="G7" t="n">
-        <v>756</v>
+        <v>787</v>
       </c>
       <c r="H7" t="n">
         <v>1.29</v>
@@ -1079,23 +1079,23 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-12000</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>WCLC 세계폐암학회에서의 센딥 파텔 교수 데이터 발표에 따른 주가 대폭등 예고. 기술 수출 기대감.</t>
+          <t>폐암학회 데이터 발표 기대감으로 인한 주가 급등 전망. 기술 수출 가능성 및 텐버거 성장주 부각.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['폐암학회', '기술수출', '임상']</t>
+          <t>['폐암학회', '데이터발표', '기술수출']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1931</v>
+        <v>1927</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+9.72%</t>
+          <t>+9.49%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>110</v>
       </c>
       <c r="F8" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H8" t="n">
         <v>2.44</v>
@@ -1162,7 +1162,7 @@
         <v>2.12</v>
       </c>
       <c r="O8" t="n">
-        <v>39323000000</v>
+        <v>39568000000</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>홍해 지정학적 리스크 및 유가 상승에 따른 전쟁 테마주 분류. 장금상선 지분율 언급.</t>
+          <t>이란 테마주 연계 급등 기대감 속 차익실현 매물 출현. 유가 상승 및 지정학적 리스크로 인한 수혜 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['전쟁테마', '유가상승', '장금상선']</t>
+          <t>['전쟁테마주', '유가상승', '정유업계']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,79 +1207,79 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7680</v>
+        <v>9970</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+8.17%</t>
+          <t>+7.44%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="F9" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="G9" t="n">
-        <v>353</v>
+        <v>302</v>
       </c>
       <c r="H9" t="n">
-        <v>11.72</v>
+        <v>4.49</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>7100</v>
+        <v>9280</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>10030</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>10880</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>9800</v>
       </c>
       <c r="N9" t="n">
-        <v>11.62</v>
+        <v>4.42</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>20620041550</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>15640</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5470</v>
       </c>
       <c r="R9" t="n">
-        <v>43000</v>
+        <v>-88000</v>
       </c>
       <c r="S9" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>내일 주가 상승에 대한 기대감과 함께 기관 매수세 및 굿뉴스 언급이 있으나, 주가 상승 저해 요인 및 공매도 관련 내용으로 상쇄되어 구체적 근거는 미흡.</t>
+          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['대차', '공매도', '주포']</t>
+          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,43 +1287,43 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>064550</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>416500</v>
+        <v>53000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>+2.32%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.2</v>
+        <v>-0.44</v>
       </c>
       <c r="E10" t="n">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="F10" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>216</v>
+        <v>131</v>
       </c>
       <c r="H10" t="n">
-        <v>38.02</v>
+        <v>2.92</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,47 +1331,47 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>415500</v>
+        <v>51800</v>
       </c>
       <c r="K10" t="n">
-        <v>407000</v>
+        <v>51300</v>
       </c>
       <c r="L10" t="n">
-        <v>418000</v>
+        <v>54500</v>
       </c>
       <c r="M10" t="n">
-        <v>404000</v>
+        <v>51300</v>
       </c>
       <c r="N10" t="n">
-        <v>37.82</v>
+        <v>3.36</v>
       </c>
       <c r="O10" t="n">
-        <v>45603972750</v>
+        <v>87829035850</v>
       </c>
       <c r="P10" t="n">
-        <v>822000</v>
+        <v>87700</v>
       </c>
       <c r="Q10" t="n">
-        <v>283000</v>
+        <v>17210</v>
       </c>
       <c r="R10" t="n">
-        <v>13000</v>
+        <v>116000</v>
       </c>
       <c r="S10" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>로봇 부품 사업 확장 및 글로벌 수주 기대감, 유럽 중국차 관세 이슈 반사이익 전망.</t>
+          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['로봇', '수주', '미래차']</t>
+          <t>['태양광', '고유가', '신호가']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,115 +1379,115 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>475150</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>53200</v>
+        <v>26600</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+1.92%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.44</v>
+        <v>-0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>257</v>
       </c>
       <c r="F11" t="n">
-        <v>39</v>
+        <v>125</v>
       </c>
       <c r="G11" t="n">
-        <v>128</v>
+        <v>435</v>
       </c>
       <c r="H11" t="n">
-        <v>2.92</v>
+        <v>0.32</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>53200</v>
+        <v>26100</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>26350</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>30300</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>25400</v>
       </c>
       <c r="N11" t="n">
-        <v>3.36</v>
+        <v>0.33</v>
       </c>
       <c r="O11" t="n">
-        <v>85949000000</v>
+        <v>308995170875</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>39350</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="R11" t="n">
-        <v>116000</v>
+        <v>7000</v>
       </c>
       <c r="S11" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
+          <t>타 급등주 대비 상대적 선방 및 외인 유입 기대감 형성. 시장 하락장 속 방어적 흐름.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['태양광', '고유가', '신호가']</t>
+          <t>['급등주', '외국인유입', '하락장']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>89900</v>
+        <v>50400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1495,19 +1495,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.06</v>
+        <v>0.09</v>
       </c>
       <c r="E12" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="F12" t="n">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="G12" t="n">
-        <v>784</v>
+        <v>540</v>
       </c>
       <c r="H12" t="n">
-        <v>23.59</v>
+        <v>38.78</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>89900</v>
+        <v>50400</v>
       </c>
       <c r="K12" t="n">
-        <v>88700</v>
+        <v>50500</v>
       </c>
       <c r="L12" t="n">
-        <v>91000</v>
+        <v>51200</v>
       </c>
       <c r="M12" t="n">
-        <v>88000</v>
+        <v>49650</v>
       </c>
       <c r="N12" t="n">
-        <v>23.65</v>
+        <v>38.69</v>
       </c>
       <c r="O12" t="n">
-        <v>122559679800</v>
+        <v>56234463525</v>
       </c>
       <c r="P12" t="n">
-        <v>139200</v>
+        <v>67300</v>
       </c>
       <c r="Q12" t="n">
-        <v>57000</v>
+        <v>23150</v>
       </c>
       <c r="R12" t="n">
-        <v>-264000</v>
+        <v>-134000</v>
       </c>
       <c r="S12" t="n">
-        <v>26000</v>
+        <v>2000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 투자 협상 마무리 및 중동 에너지 공급망 이슈에 따른 두산에너빌리티의 수혜 기대. 수주 잔고 언급.</t>
+          <t>약 4.7조원 규모의 대규모 수주 공시로 인한 긍정적 시장 반응 및 상승 추세 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['원전', '에너지 공급망', '수주 잔고']</t>
+          <t>['수주', '공시', '추세']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1853000</v>
+        <v>415000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.12</v>
+        <v>0.2</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>87</v>
       </c>
       <c r="F13" t="n">
-        <v>459</v>
+        <v>46</v>
       </c>
       <c r="G13" t="n">
-        <v>1342</v>
+        <v>219</v>
       </c>
       <c r="H13" t="n">
-        <v>50.55</v>
+        <v>38.02</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1856000</v>
+        <v>415500</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>407000</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>418000</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>404000</v>
       </c>
       <c r="N13" t="n">
-        <v>50.67</v>
+        <v>37.82</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>46434576250</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>822000</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>283000</v>
       </c>
       <c r="R13" t="n">
-        <v>-249000</v>
+        <v>13000</v>
       </c>
       <c r="S13" t="n">
-        <v>-102000</v>
+        <v>1000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>종목 하락 속에서 일부 긍정적 기대와 함께 개인 투자자 매수세 언급이 있으나, 구체적인 호재나 하락 원인 분석 등 객관적 근거는 부족.</t>
+          <t>로봇 부품 사업 확장 및 글로벌 수주 기대감, 유럽 중국차 관세 이슈 반사이익 전망.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['개인투자자', '금리', '박스권']</t>
+          <t>['로봇', '수주', '미래차']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>012330</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>50400</v>
+        <v>89600</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>138</v>
+        <v>203</v>
       </c>
       <c r="F14" t="n">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="G14" t="n">
-        <v>534</v>
+        <v>796</v>
       </c>
       <c r="H14" t="n">
-        <v>38.78</v>
+        <v>23.59</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>50800</v>
+        <v>89900</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>88700</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>91000</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="N14" t="n">
-        <v>38.69</v>
+        <v>23.65</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>127418578400</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>139200</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="R14" t="n">
-        <v>-134000</v>
+        <v>-264000</v>
       </c>
       <c r="S14" t="n">
-        <v>2000</v>
+        <v>26000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>약 4.7조원 규모의 대규모 수주 공시로 인한 긍정적 시장 반응 및 상승 추세 기대.</t>
+          <t>미국 투자 협상 마무리 및 중동 에너지 공급망 이슈에 따른 두산에너빌리티의 수혜 기대. 수주 잔고 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['수주', '공시', '추세']</t>
+          <t>['원전', '에너지 공급망', '수주 잔고']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1774,13 +1774,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G15" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H15" t="n">
         <v>25.55</v>
@@ -1851,83 +1851,83 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19550</v>
+        <v>14120</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.01%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.01</v>
+        <v>-0.11</v>
       </c>
       <c r="E16" t="n">
-        <v>128</v>
+        <v>91</v>
       </c>
       <c r="F16" t="n">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="G16" t="n">
-        <v>443</v>
+        <v>501</v>
       </c>
       <c r="H16" t="n">
-        <v>10.65</v>
+        <v>5.98</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>19750</v>
+        <v>14320</v>
       </c>
       <c r="K16" t="n">
-        <v>19500</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>19840</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>19060</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>10.64</v>
+        <v>6.09</v>
       </c>
       <c r="O16" t="n">
-        <v>83905239500</v>
+        <v>89436000000</v>
       </c>
       <c r="P16" t="n">
-        <v>40350</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3320</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>-371000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-69000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>대차해지 및 공매도 관련 언급 다수. NH 투자증권 목표가 상향 뉴스 언급.</t>
+          <t>원전 섹터 부각 및 120일선 지지 기대감. 모건 스탠리 대량 매도 이슈 관찰.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '목표가상향']</t>
+          <t>['원전', '120일선', '모건스탠리']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,90 +1936,90 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14160</v>
+        <v>19420</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>-1.67%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.11</v>
+        <v>0.01</v>
       </c>
       <c r="E17" t="n">
-        <v>94</v>
+        <v>129</v>
       </c>
       <c r="F17" t="n">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="G17" t="n">
-        <v>498</v>
+        <v>454</v>
       </c>
       <c r="H17" t="n">
-        <v>5.98</v>
+        <v>10.65</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>14320</v>
+        <v>19750</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>19500</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>19840</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>19060</v>
       </c>
       <c r="N17" t="n">
-        <v>6.09</v>
+        <v>10.64</v>
       </c>
       <c r="O17" t="n">
-        <v>88263000000</v>
+        <v>86162414170</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>40350</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3320</v>
       </c>
       <c r="R17" t="n">
-        <v>-371000</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-69000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>원자력 발전 섹터 관련 긍정적 전망. 모건 스탠리 매수세 및 120일선 지지 언급.</t>
+          <t>대차 해지 및 공매도 세력 저항 촉구. 목표가 상향 뉴스 및 해외 투자 기대감 형성.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['원전', '모건스탠리', '120일선']</t>
+          <t>['대차해지', '공매도', '목표가상향']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8820</v>
+        <v>8800</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>-1.68%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F18" t="n">
         <v>50</v>
       </c>
       <c r="G18" t="n">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="H18" t="n">
         <v>27.19</v>
@@ -2082,7 +2082,7 @@
         <v>27.16</v>
       </c>
       <c r="O18" t="n">
-        <v>15012000000</v>
+        <v>15206000000</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>경영 성과 및 주가 하락에 대한 강한 불만 표출. 목표 주가 하향 전망.</t>
+          <t>수년간 누적된 막대한 경영 손실에 대한 불만 고조. 주가 부양 기대감 약화.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['경영성과', '주가하락', '목표주가']</t>
+          <t>['경영손실', '주가부양', '실적악화']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14770</v>
+        <v>14690</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>-2.33%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F19" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G19" t="n">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2174,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>17766360735</v>
+        <v>18088831500</v>
       </c>
       <c r="P19" t="n">
         <v>19380</v>
@@ -2219,83 +2219,83 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14180</v>
+        <v>192500</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.80%</t>
+          <t>-2.53%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.39</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F20" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G20" t="n">
-        <v>231</v>
+        <v>130</v>
       </c>
       <c r="H20" t="n">
-        <v>2.5</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>14740</v>
+        <v>197500</v>
       </c>
       <c r="K20" t="n">
-        <v>14050</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>14560</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>14030</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.89</v>
+        <v>75.92</v>
       </c>
       <c r="O20" t="n">
-        <v>50640476760</v>
+        <v>389827000000</v>
       </c>
       <c r="P20" t="n">
-        <v>31500</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1272</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>-128000</v>
+        <v>-852000</v>
       </c>
       <c r="S20" t="n">
-        <v>-6000</v>
+        <v>-123000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>광통신 사업 및 미국 시장 진출 기대감. 외국인 매수세 유입에 따른 주가 상승 전망.</t>
+          <t>기관 및 외국인 매도세 지속, 주가 하락에 대한 불안감과 특별 배당 기대감 혼재.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['광통신', '미국진출', '외국인']</t>
+          <t>['기관매도', '주가하락', '특별배당']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,130 +2304,130 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>257250</v>
+        <v>12680</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-4.37%</t>
+          <t>-2.69%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.1</v>
+        <v>0.8</v>
       </c>
       <c r="E21" t="n">
-        <v>800</v>
+        <v>71</v>
       </c>
       <c r="F21" t="n">
-        <v>512</v>
+        <v>42</v>
       </c>
       <c r="G21" t="n">
-        <v>1585</v>
+        <v>73</v>
       </c>
       <c r="H21" t="n">
-        <v>46.71</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>269000</v>
+        <v>13030</v>
       </c>
       <c r="K21" t="n">
-        <v>258000</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>261000</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>257000</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>46.81</v>
+        <v>0.14</v>
       </c>
       <c r="O21" t="n">
-        <v>2011543820250</v>
+        <v>50014000000</v>
       </c>
       <c r="P21" t="n">
-        <v>374500</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>72100</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>-1232000</v>
+        <v>-69000</v>
       </c>
       <c r="S21" t="n">
-        <v>-646000</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>반도체 수출 호조에도 불구하고 주가 부진. 정치적 이슈와 엮이며 개인 투자자 불만 토로.</t>
+          <t>원전 테마주로서의 삼미금속 언급. 한전기술 등 타 원전주들의 급등 속 상대적 부진 및 거래량 부족에 대한 지적.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['반도체수출', '주가부진', '정치이슈']</t>
+          <t>['원전', '테마주', '거래량']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>104</v>
+        <v>5</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>192700</v>
+        <v>7390</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-5.07%</t>
+          <t>-3.78%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="E22" t="n">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="F22" t="n">
         <v>57</v>
       </c>
       <c r="G22" t="n">
-        <v>130</v>
+        <v>362</v>
       </c>
       <c r="H22" t="n">
-        <v>75.98999999999999</v>
+        <v>11.72</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,38 +2435,38 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>203000</v>
+        <v>7680</v>
       </c>
       <c r="K22" t="n">
-        <v>195000</v>
+        <v>7540</v>
       </c>
       <c r="L22" t="n">
-        <v>195600</v>
+        <v>7660</v>
       </c>
       <c r="M22" t="n">
-        <v>191000</v>
+        <v>7370</v>
       </c>
       <c r="N22" t="n">
-        <v>75.92</v>
+        <v>11.62</v>
       </c>
       <c r="O22" t="n">
-        <v>382125511400</v>
+        <v>8770439765</v>
       </c>
       <c r="P22" t="n">
-        <v>243500</v>
+        <v>8850</v>
       </c>
       <c r="Q22" t="n">
-        <v>58600</v>
+        <v>4220</v>
       </c>
       <c r="R22" t="n">
-        <v>-852000</v>
+        <v>43000</v>
       </c>
       <c r="S22" t="n">
-        <v>-123000</v>
+        <v>-2000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>기관 및 외국인 매도세 지속, 주가 하락에 대한 불안감과 특별 배당 기대감 혼재.</t>
+          <t>기관 매수세 유입 기대감 및 공매도 부담 경감. 단기적 지지 구간에서의 횡보 관찰.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,11 +2475,11 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['기관매도', '주가하락', '특별배당']</t>
+          <t>['기관매수', '공매도', '지지구간']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,261 +2488,261 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12360</v>
+        <v>1777000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-5.14%</t>
+          <t>-4.10%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.8</v>
+        <v>-0.12</v>
       </c>
       <c r="E23" t="n">
-        <v>68</v>
+        <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>42</v>
+        <v>455</v>
       </c>
       <c r="G23" t="n">
-        <v>62</v>
+        <v>1401</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9399999999999999</v>
+        <v>50.55</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>13030</v>
+        <v>1853000</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1773000</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1795000</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1768000</v>
       </c>
       <c r="N23" t="n">
-        <v>0.14</v>
+        <v>50.67</v>
       </c>
       <c r="O23" t="n">
-        <v>40566000000</v>
+        <v>2707051284000</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2987000</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>305500</v>
       </c>
       <c r="R23" t="n">
-        <v>-69000</v>
+        <v>-249000</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>-102000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>원전 테마주로서의 삼미금속 언급. 한전기술 등 타 원전주들의 급등 속 상대적 부진 및 거래량 부족에 대한 지적.</t>
+          <t>반도체 섹터 전반의 하락세 속 약세 지속. 시장 불확실성으로 인한 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['원전', '테마주', '거래량']</t>
+          <t>['반도체', '금리인상', '하락세']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9280</v>
+        <v>257000</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-5.31%</t>
+          <t>-4.46%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="E24" t="n">
-        <v>67</v>
+        <v>800</v>
       </c>
       <c r="F24" t="n">
-        <v>40</v>
+        <v>507</v>
       </c>
       <c r="G24" t="n">
-        <v>296</v>
+        <v>1668</v>
       </c>
       <c r="H24" t="n">
-        <v>4.49</v>
+        <v>46.71</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>9800</v>
+        <v>269000</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>258000</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>261000</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>256500</v>
       </c>
       <c r="N24" t="n">
-        <v>4.42</v>
+        <v>46.81</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2161195171500</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>374500</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>72100</v>
       </c>
       <c r="R24" t="n">
-        <v>-88000</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
+          <t>반도체 수출 역대 최대 기록에도 주가 하락세 지속. 정치적 이슈와 맞물린 시장 불확실성 증폭.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
+          <t>['반도체 수출', '국정지지율', '정치이슈']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>2</v>
+        <v>104</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>233000</v>
+        <v>14160</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-7.91%</t>
+          <t>-5.35%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.96</v>
+        <v>-0.39</v>
       </c>
       <c r="E25" t="n">
-        <v>217</v>
+        <v>90</v>
       </c>
       <c r="F25" t="n">
-        <v>107</v>
+        <v>52</v>
       </c>
       <c r="G25" t="n">
-        <v>744</v>
+        <v>233</v>
       </c>
       <c r="H25" t="n">
-        <v>7.58</v>
+        <v>2.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>253000</v>
+        <v>14960</v>
       </c>
       <c r="K25" t="n">
-        <v>241000</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>241000</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>231000</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>8.539999999999999</v>
+        <v>2.89</v>
       </c>
       <c r="O25" t="n">
-        <v>167391586000</v>
+        <v>52807000000</v>
       </c>
       <c r="P25" t="n">
-        <v>426000</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>86100</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>-298000</v>
+        <v>-128000</v>
       </c>
       <c r="S25" t="n">
-        <v>-18000</v>
+        <v>-6000</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>9월 TC본더 수출 데이터 관련 언급과 공매도 관련 내용이 있으나, 주가 방어 및 회사 차원의 소각/무증 발표 요구 등 감정적이고 구체적 근거가 부족한 내용이 혼재.</t>
+          <t>광통신 사업 및 미국 시장 진출 기대감. 외국인 매수세 유입에 따른 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
@@ -2751,11 +2751,11 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['TC본더', '공매도', '소각']</t>
+          <t>['광통신', '미국진출', '외국인']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3555</v>
+        <v>3550</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-8.02%</t>
+          <t>-8.15%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>-0.8100000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F26" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G26" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="H26" t="n">
         <v>0.73</v>
@@ -2818,7 +2818,7 @@
         <v>1.54</v>
       </c>
       <c r="O26" t="n">
-        <v>40318000000</v>
+        <v>40509000000</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2827,7 +2827,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>64000</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -2863,83 +2863,83 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26800</v>
+        <v>232000</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-11.55%</t>
+          <t>-8.30%</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-0.01</v>
+        <v>-0.96</v>
       </c>
       <c r="E27" t="n">
-        <v>247</v>
+        <v>221</v>
       </c>
       <c r="F27" t="n">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="G27" t="n">
-        <v>427</v>
+        <v>768</v>
       </c>
       <c r="H27" t="n">
-        <v>0.32</v>
+        <v>7.58</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>30300</v>
+        <v>253000</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>241000</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>241000</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>231000</v>
       </c>
       <c r="N27" t="n">
-        <v>0.33</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>303142000000</v>
+        <v>170782942000</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>426000</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>86100</v>
       </c>
       <c r="R27" t="n">
-        <v>7000</v>
+        <v>-298000</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>-18000</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>급등주로서의 기대감과 변동성에 대한 언급. 투자자들의 심리적 동요 관찰.</t>
+          <t>9월 TC본더 수출 데이터 관련 언급과 공매도 관련 내용이 있으나, 주가 방어 및 회사 차원의 소각/무증 발표 요구 등 감정적이고 구체적 근거가 부족한 내용이 혼재.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['급등주', '변동성', '투자심리']</t>
+          <t>['TC본더', '공매도', '소각']</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>042700</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260911_12.xlsx
+++ b/data/trending_integrated_20260911_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15680</v>
+        <v>15560</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+29.69%</t>
+          <t>+28.70%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>3.11</v>
       </c>
       <c r="E2" t="n">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="F2" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G2" t="n">
-        <v>845</v>
+        <v>864</v>
       </c>
       <c r="H2" t="n">
         <v>3.14</v>
@@ -610,7 +610,7 @@
         <v>0.03</v>
       </c>
       <c r="O2" t="n">
-        <v>184686000000</v>
+        <v>185989000000</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>국제 유가 급등 및 중동 지정학적 리스크 부각. 3연상 및 15,000원 지지선 돌파 기대.</t>
+          <t>국제 유가 급등에 따른 급등세. 사우디, 중동 전쟁 관련 호재 및 외국인 대량 매수 유입.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['국제유가', '지정학적리스크', '3연상']</t>
+          <t>['국제 유가', '중동 전쟁', '외국인 매수']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,10 +670,10 @@
         <v>-0.22</v>
       </c>
       <c r="E3" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F3" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G3" t="n">
         <v>130</v>
@@ -702,7 +702,7 @@
         <v>2.61</v>
       </c>
       <c r="O3" t="n">
-        <v>207310000000</v>
+        <v>207402000000</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2555</v>
+        <v>2565</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+20.24%</t>
+          <t>+20.14%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F4" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G4" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H4" t="n">
         <v>3.83</v>
@@ -779,28 +779,28 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2125</v>
+        <v>2135</v>
       </c>
       <c r="K4" t="n">
-        <v>2230</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2692</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2170</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>3.76</v>
       </c>
       <c r="O4" t="n">
-        <v>92680046820</v>
+        <v>93527000000</v>
       </c>
       <c r="P4" t="n">
-        <v>4810</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>-1884000</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>양자컴퓨터 및 사이버 보안 테마 연계 기대감 속 변동성 확대. 외국인 및 기관 매도세 관찰.</t>
+          <t>양자컴퓨터 및 사이버 보안 테마 관련 언급. 외국인 및 프로그램 매도 물량 출회.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['양자컴퓨터', '사이버보안', '외국인매도']</t>
+          <t>['양자컴퓨터', '사이버 보안', '외국인 매도']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>137600</v>
+        <v>137800</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+18.93%</t>
+          <t>+19.10%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.26</v>
       </c>
       <c r="E5" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="F5" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G5" t="n">
-        <v>230</v>
+        <v>257</v>
       </c>
       <c r="H5" t="n">
         <v>4.32</v>
@@ -886,7 +886,7 @@
         <v>4.58</v>
       </c>
       <c r="O5" t="n">
-        <v>436463437500</v>
+        <v>438909664100</v>
       </c>
       <c r="P5" t="n">
         <v>196800</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>거래량 부진 속 애플 관련 호재 가능성 언급. 단기 급등 기대와 경계 혼재.</t>
+          <t>매출 호조 및 애플 관련 호재 가능성 언급. 거래량 부족 및 단기 급등에 대한 경계심 혼재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['거래량', '애플', '단기급등']</t>
+          <t>['매출 호조', '애플', '거래량']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7720</v>
+        <v>7690</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+15.22%</t>
+          <t>+17.05%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.79</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F6" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G6" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="H6" t="n">
         <v>2.15</v>
@@ -963,28 +963,28 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6700</v>
+        <v>6570</v>
       </c>
       <c r="K6" t="n">
-        <v>6530</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>8370</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>6430</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>2.94</v>
       </c>
       <c r="O6" t="n">
-        <v>146656276545</v>
+        <v>148139000000</v>
       </c>
       <c r="P6" t="n">
-        <v>16200</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1206</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>141000</v>
@@ -1038,13 +1038,13 @@
         <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F7" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G7" t="n">
-        <v>787</v>
+        <v>804</v>
       </c>
       <c r="H7" t="n">
         <v>1.29</v>
@@ -1079,23 +1079,23 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-12000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>폐암학회 데이터 발표 기대감으로 인한 주가 급등 전망. 기술 수출 가능성 및 텐버거 성장주 부각.</t>
+          <t>9월 14일 WCLC(세계폐암학회)에서의 센딥파텔 교수 데이터 발표에 따른 주가 대폭등 예고. 기술 수출 및 글로벌 빅파마와의 협력 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['폐암학회', '데이터발표', '기술수출']</t>
+          <t>['WCLC', '폐암학회', '기술 수출']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1927</v>
+        <v>1921</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+9.49%</t>
+          <t>+9.15%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.32</v>
       </c>
       <c r="E8" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F8" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G8" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H8" t="n">
         <v>2.44</v>
@@ -1162,7 +1162,7 @@
         <v>2.12</v>
       </c>
       <c r="O8" t="n">
-        <v>39568000000</v>
+        <v>39793000000</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1211,18 +1211,18 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9970</v>
+        <v>9990</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+7.44%</t>
+          <t>+7.65%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F9" t="n">
         <v>40</v>
@@ -1254,7 +1254,7 @@
         <v>4.42</v>
       </c>
       <c r="O9" t="n">
-        <v>20620041550</v>
+        <v>20691356750</v>
       </c>
       <c r="P9" t="n">
         <v>15640</v>
@@ -1299,175 +1299,175 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53000</v>
+        <v>26650</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+2.32%</t>
+          <t>+2.11%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.44</v>
+        <v>-0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>68</v>
+        <v>270</v>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>131</v>
       </c>
       <c r="G10" t="n">
-        <v>131</v>
+        <v>443</v>
       </c>
       <c r="H10" t="n">
-        <v>2.92</v>
+        <v>0.32</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>51800</v>
+        <v>26100</v>
       </c>
       <c r="K10" t="n">
-        <v>51300</v>
+        <v>26350</v>
       </c>
       <c r="L10" t="n">
-        <v>54500</v>
+        <v>30300</v>
       </c>
       <c r="M10" t="n">
-        <v>51300</v>
+        <v>25400</v>
       </c>
       <c r="N10" t="n">
-        <v>3.36</v>
+        <v>0.33</v>
       </c>
       <c r="O10" t="n">
-        <v>87829035850</v>
+        <v>311060225850</v>
       </c>
       <c r="P10" t="n">
-        <v>87700</v>
+        <v>39350</v>
       </c>
       <c r="Q10" t="n">
-        <v>17210</v>
+        <v>8200</v>
       </c>
       <c r="R10" t="n">
-        <v>116000</v>
+        <v>7000</v>
       </c>
       <c r="S10" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
+          <t>타 급등주 대비 상대적 선방 및 외인 유입 기대감 형성. 시장 하락장 속 방어적 흐름.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['태양광', '고유가', '신호가']</t>
+          <t>['급등주', '외국인유입', '하락장']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26600</v>
+        <v>253000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+1.92%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.01</v>
+        <v>-0.96</v>
       </c>
       <c r="E11" t="n">
-        <v>257</v>
+        <v>223</v>
       </c>
       <c r="F11" t="n">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="G11" t="n">
-        <v>435</v>
+        <v>787</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32</v>
+        <v>7.58</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>26100</v>
+        <v>250500</v>
       </c>
       <c r="K11" t="n">
-        <v>26350</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>30300</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>25400</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0.33</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>308995170875</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>39350</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>8200</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>7000</v>
+        <v>-298000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-18000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>타 급등주 대비 상대적 선방 및 외인 유입 기대감 형성. 시장 하락장 속 방어적 흐름.</t>
+          <t>9월 TC 본더 수출 데이터 및 반도체 수출 증가 뉴스 언급. 기관 매수세 확인 및 공매도 청산 요구.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['급등주', '외국인유입', '하락장']</t>
+          <t>['TC본더', '공매도', '수출 데이터']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50400</v>
+        <v>90000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>140</v>
+        <v>206</v>
       </c>
       <c r="F12" t="n">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="G12" t="n">
-        <v>540</v>
+        <v>803</v>
       </c>
       <c r="H12" t="n">
-        <v>38.78</v>
+        <v>23.59</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>50400</v>
+        <v>89900</v>
       </c>
       <c r="K12" t="n">
-        <v>50500</v>
+        <v>88700</v>
       </c>
       <c r="L12" t="n">
-        <v>51200</v>
+        <v>91000</v>
       </c>
       <c r="M12" t="n">
-        <v>49650</v>
+        <v>88000</v>
       </c>
       <c r="N12" t="n">
-        <v>38.69</v>
+        <v>23.65</v>
       </c>
       <c r="O12" t="n">
-        <v>56234463525</v>
+        <v>132594758500</v>
       </c>
       <c r="P12" t="n">
-        <v>67300</v>
+        <v>139200</v>
       </c>
       <c r="Q12" t="n">
-        <v>23150</v>
+        <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>-134000</v>
+        <v>-264000</v>
       </c>
       <c r="S12" t="n">
-        <v>2000</v>
+        <v>26000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>약 4.7조원 규모의 대규모 수주 공시로 인한 긍정적 시장 반응 및 상승 추세 기대.</t>
+          <t>미국 투자 협상 마무리 및 중동 에너지 공급망 이슈에 따른 두산에너빌리티의 수혜 기대. 수주 잔고 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['수주', '공시', '추세']</t>
+          <t>['원전', '에너지 공급망', '수주 잔고']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1590,13 +1590,13 @@
         <v>0.2</v>
       </c>
       <c r="E13" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F13" t="n">
         <v>46</v>
       </c>
       <c r="G13" t="n">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="H13" t="n">
         <v>38.02</v>
@@ -1622,7 +1622,7 @@
         <v>37.82</v>
       </c>
       <c r="O13" t="n">
-        <v>46434576250</v>
+        <v>47169884250</v>
       </c>
       <c r="P13" t="n">
         <v>822000</v>
@@ -1631,23 +1631,23 @@
         <v>283000</v>
       </c>
       <c r="R13" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>로봇 부품 사업 확장 및 글로벌 수주 기대감, 유럽 중국차 관세 이슈 반사이익 전망.</t>
+          <t>미래차 및 로봇 신기술 공개 및 수주 소식. 그룹사 양산 로드맵 가동 및 대차상환 후 순매수 유입.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['로봇', '수주', '미래차']</t>
+          <t>['미래차', '로봇 신기술', '수주']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>89600</v>
+        <v>1853000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.06</v>
+        <v>-0.12</v>
       </c>
       <c r="E14" t="n">
-        <v>203</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>118</v>
+        <v>448</v>
       </c>
       <c r="G14" t="n">
-        <v>796</v>
+        <v>1493</v>
       </c>
       <c r="H14" t="n">
-        <v>23.59</v>
+        <v>50.55</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>89900</v>
+        <v>1856000</v>
       </c>
       <c r="K14" t="n">
-        <v>88700</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>91000</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>23.65</v>
+        <v>50.67</v>
       </c>
       <c r="O14" t="n">
-        <v>127418578400</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>139200</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-264000</v>
+        <v>-249000</v>
       </c>
       <c r="S14" t="n">
-        <v>26000</v>
+        <v>-102000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 투자 협상 마무리 및 중동 에너지 공급망 이슈에 따른 두산에너빌리티의 수혜 기대. 수주 잔고 언급.</t>
+          <t>미국장 대비 선방 중이나, 향후 하이닉스의 영업이익 전망에 대한 부정적 의견 존재. 개인 투자자 매수세 및 유가, 금리 변동성 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전', '에너지 공급망', '수주 잔고']</t>
+          <t>['영업이익', '개인투자자', '금리']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29550</v>
+        <v>52800</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>-0.75%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.44</v>
       </c>
       <c r="E15" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="F15" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G15" t="n">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="H15" t="n">
-        <v>25.55</v>
+        <v>2.92</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>29800</v>
+        <v>53200</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1803,10 +1803,10 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>24.99</v>
+        <v>3.36</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>89412000000</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1815,14 +1815,14 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>265000</v>
+        <v>116000</v>
       </c>
       <c r="S15" t="n">
-        <v>-69000</v>
+        <v>10000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
+          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['유럽 자금', '환율', '유가']</t>
+          <t>['태양광', '고유가', '신호가']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,46 +1844,46 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>475150</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14120</v>
+        <v>50400</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.11</v>
+        <v>0.09</v>
       </c>
       <c r="E16" t="n">
-        <v>91</v>
+        <v>142</v>
       </c>
       <c r="F16" t="n">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="G16" t="n">
-        <v>501</v>
+        <v>546</v>
       </c>
       <c r="H16" t="n">
-        <v>5.98</v>
+        <v>38.78</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>14320</v>
+        <v>50800</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1895,10 +1895,10 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>6.09</v>
+        <v>38.69</v>
       </c>
       <c r="O16" t="n">
-        <v>89436000000</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1907,27 +1907,27 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-371000</v>
+        <v>-134000</v>
       </c>
       <c r="S16" t="n">
-        <v>-69000</v>
+        <v>2000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>원전 섹터 부각 및 120일선 지지 기대감. 모건 스탠리 대량 매도 이슈 관찰.</t>
+          <t>약 4.7조원 규모의 대규모 수주 공시로 인한 긍정적 시장 반응 및 상승 추세 기대.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['원전', '120일선', '모건스탠리']</t>
+          <t>['수주', '공시', '추세']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19420</v>
+        <v>19570</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.67%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1964,7 +1964,7 @@
         <v>79</v>
       </c>
       <c r="G17" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="H17" t="n">
         <v>10.65</v>
@@ -1990,7 +1990,7 @@
         <v>10.64</v>
       </c>
       <c r="O17" t="n">
-        <v>86162414170</v>
+        <v>87873388835</v>
       </c>
       <c r="P17" t="n">
         <v>40350</v>
@@ -1999,14 +1999,14 @@
         <v>3320</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>-233000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-16000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>대차 해지 및 공매도 세력 저항 촉구. 목표가 상향 뉴스 및 해외 투자 기대감 형성.</t>
+          <t>대차해지 독려 및 목표가 상향 뉴스 언급. 공매도 세력과의 대립 구도 형성.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '목표가상향']</t>
+          <t>['대차해지', '목표가 상향', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,39 +2035,39 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8800</v>
+        <v>14130</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.68%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.03</v>
+        <v>-0.11</v>
       </c>
       <c r="E18" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="F18" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G18" t="n">
-        <v>240</v>
+        <v>548</v>
       </c>
       <c r="H18" t="n">
-        <v>27.19</v>
+        <v>5.98</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>8950</v>
+        <v>14320</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2079,10 +2079,10 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>27.16</v>
+        <v>6.09</v>
       </c>
       <c r="O18" t="n">
-        <v>15206000000</v>
+        <v>90412000000</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -2091,27 +2091,27 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-100000</v>
+        <v>-371000</v>
       </c>
       <c r="S18" t="n">
-        <v>-78000</v>
+        <v>-69000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>수년간 누적된 막대한 경영 손실에 대한 불만 고조. 주가 부양 기대감 약화.</t>
+          <t>원전 관련 섹터 상승 기대감 및 공매도 세력과의 갈등 양상. 모건 증권의 대량 매도 물량 출회.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['경영손실', '주가부양', '실적악화']</t>
+          <t>['원전', '공매도', '모건 증권']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14690</v>
+        <v>8800</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.33%</t>
+          <t>-1.68%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="E19" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="F19" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="G19" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>27.19</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,91 +2159,91 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>15040</v>
+        <v>8950</v>
       </c>
       <c r="K19" t="n">
-        <v>14550</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>15260</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>14350</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>27.16</v>
       </c>
       <c r="O19" t="n">
-        <v>18088831500</v>
+        <v>15409000000</v>
       </c>
       <c r="P19" t="n">
-        <v>19380</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>금호건설, 호남 반도체 부지 100만평 추가 확보 검토 및 삼성전자 신축 공장 수주 소식. 친환경 및 폐기물 처리 사업 관련 성장성 기대.</t>
+          <t>회사의 경영 실적 악화 및 주가 부진에 대한 불만 고조. 기술적 반등 기대감도 낮음.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['반도체 부지', '신축 공장 수주', '친환경']</t>
+          <t>['경영 실적', '주가 부진', '기술적 반등']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>192500</v>
+        <v>14720</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.53%</t>
+          <t>-2.13%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="F20" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="G20" t="n">
-        <v>130</v>
+        <v>245</v>
       </c>
       <c r="H20" t="n">
-        <v>75.98999999999999</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,99 +2251,99 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>197500</v>
+        <v>15040</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>14550</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>15260</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>14350</v>
       </c>
       <c r="N20" t="n">
-        <v>75.92</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>389827000000</v>
+        <v>18496884070</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>19380</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="R20" t="n">
-        <v>-852000</v>
+        <v>22000</v>
       </c>
       <c r="S20" t="n">
-        <v>-123000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>기관 및 외국인 매도세 지속, 주가 하락에 대한 불안감과 특별 배당 기대감 혼재.</t>
+          <t>금호건설, 호남 반도체 부지 100만평 추가 확보 검토 및 삼성전자 신축 공장 수주 소식. 친환경 및 폐기물 처리 사업 관련 성장성 기대.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['기관매도', '주가하락', '특별배당']</t>
+          <t>['반도체 부지', '신축 공장 수주', '친환경']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12680</v>
+        <v>192900</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.69%</t>
+          <t>-2.33%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.8</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="F21" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="G21" t="n">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9399999999999999</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>13030</v>
+        <v>197500</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2355,10 +2355,10 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.14</v>
+        <v>75.92</v>
       </c>
       <c r="O21" t="n">
-        <v>50014000000</v>
+        <v>395413000000</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2367,67 +2367,67 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>-69000</v>
+        <v>-852000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-123000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>원전 테마주로서의 삼미금속 언급. 한전기술 등 타 원전주들의 급등 속 상대적 부진 및 거래량 부족에 대한 지적.</t>
+          <t>연속적인 하락세와 외국인/기관 매도세 지속. 특별 배당 기대감 있으나 주가 흐름은 부정적.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전', '테마주', '거래량']</t>
+          <t>['주가 하락', '외국인 매도', '특별 배당']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7390</v>
+        <v>28650</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.78%</t>
+          <t>-3.05%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c r="F22" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="G22" t="n">
-        <v>362</v>
+        <v>140</v>
       </c>
       <c r="H22" t="n">
-        <v>11.72</v>
+        <v>51.34</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,183 +2435,183 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>7680</v>
+        <v>29550</v>
       </c>
       <c r="K22" t="n">
-        <v>7540</v>
+        <v>28650</v>
       </c>
       <c r="L22" t="n">
-        <v>7660</v>
+        <v>28900</v>
       </c>
       <c r="M22" t="n">
-        <v>7370</v>
+        <v>28500</v>
       </c>
       <c r="N22" t="n">
-        <v>11.62</v>
+        <v>24.99</v>
       </c>
       <c r="O22" t="n">
-        <v>8770439765</v>
+        <v>39929414450</v>
       </c>
       <c r="P22" t="n">
-        <v>8850</v>
+        <v>31200</v>
       </c>
       <c r="Q22" t="n">
-        <v>4220</v>
+        <v>21000</v>
       </c>
       <c r="R22" t="n">
-        <v>43000</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>기관 매수세 유입 기대감 및 공매도 부담 경감. 단기적 지지 구간에서의 횡보 관찰.</t>
+          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['기관매수', '공매도', '지지구간']</t>
+          <t>['유럽 자금', '환율', '유가']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1777000</v>
+        <v>12610</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-4.10%</t>
+          <t>-3.22%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.12</v>
+        <v>0.8</v>
       </c>
       <c r="E23" t="n">
-        <v>800</v>
+        <v>75</v>
       </c>
       <c r="F23" t="n">
-        <v>455</v>
+        <v>44</v>
       </c>
       <c r="G23" t="n">
-        <v>1401</v>
+        <v>85</v>
       </c>
       <c r="H23" t="n">
-        <v>50.55</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1853000</v>
+        <v>13030</v>
       </c>
       <c r="K23" t="n">
-        <v>1773000</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1795000</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1768000</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>50.67</v>
+        <v>0.14</v>
       </c>
       <c r="O23" t="n">
-        <v>2707051284000</v>
+        <v>54692000000</v>
       </c>
       <c r="P23" t="n">
-        <v>2987000</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>305500</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>-249000</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-102000</v>
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>반도체 섹터 전반의 하락세 속 약세 지속. 시장 불확실성으로 인한 투자 심리 위축.</t>
+          <t>원전 테마주로서의 삼미금속 언급. 한전기술 등 타 원전주들의 급등 속 상대적 부진 및 거래량 부족에 대한 지적.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['반도체', '금리인상', '하락세']</t>
+          <t>['원전', '테마주', '거래량']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>257000</v>
+        <v>7380</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-4.46%</t>
+          <t>-3.91%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="E24" t="n">
-        <v>800</v>
+        <v>120</v>
       </c>
       <c r="F24" t="n">
-        <v>507</v>
+        <v>60</v>
       </c>
       <c r="G24" t="n">
-        <v>1668</v>
+        <v>379</v>
       </c>
       <c r="H24" t="n">
-        <v>46.71</v>
+        <v>11.72</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2619,51 +2619,51 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>269000</v>
+        <v>7680</v>
       </c>
       <c r="K24" t="n">
-        <v>258000</v>
+        <v>7540</v>
       </c>
       <c r="L24" t="n">
-        <v>261000</v>
+        <v>7660</v>
       </c>
       <c r="M24" t="n">
-        <v>256500</v>
+        <v>7360</v>
       </c>
       <c r="N24" t="n">
-        <v>46.81</v>
+        <v>11.62</v>
       </c>
       <c r="O24" t="n">
-        <v>2161195171500</v>
+        <v>8992359485</v>
       </c>
       <c r="P24" t="n">
-        <v>374500</v>
+        <v>8850</v>
       </c>
       <c r="Q24" t="n">
-        <v>72100</v>
+        <v>4220</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>43000</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>반도체 수출 역대 최대 기록에도 주가 하락세 지속. 정치적 이슈와 맞물린 시장 불확실성 증폭.</t>
+          <t>금호타이어의 주가 상승 저해 요인 및 기관 매수세 가능성 언급. 삼전닉스의 부지 요구 관련 내용 포함. 공매도 단가 상승 및 주가 흐름에 대한 분석.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['반도체 수출', '국정지지율', '정치이슈']</t>
+          <t>['공매도', '기관매수', '주가흐름']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>104</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,46 +2672,46 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>14160</v>
+        <v>258000</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-5.35%</t>
+          <t>-4.27%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.39</v>
+        <v>-0.1</v>
       </c>
       <c r="E25" t="n">
-        <v>90</v>
+        <v>800</v>
       </c>
       <c r="F25" t="n">
-        <v>52</v>
+        <v>509</v>
       </c>
       <c r="G25" t="n">
-        <v>233</v>
+        <v>1671</v>
       </c>
       <c r="H25" t="n">
-        <v>2.5</v>
+        <v>46.71</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>14960</v>
+        <v>269500</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -2723,10 +2723,10 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.89</v>
+        <v>46.81</v>
       </c>
       <c r="O25" t="n">
-        <v>52807000000</v>
+        <v>2202792000000</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2735,27 +2735,27 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>-128000</v>
+        <v>-1232000</v>
       </c>
       <c r="S25" t="n">
-        <v>-6000</v>
+        <v>-646000</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>광통신 사업 및 미국 시장 진출 기대감. 외국인 매수세 유입에 따른 주가 상승 전망.</t>
+          <t>반도체 수출 최대치 기록에도 주가 하락세. 외국인 대량 매도 및 부정적 리포트 존재.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['광통신', '미국진출', '외국인']</t>
+          <t>['반도체 수출', '주가 하락', '외국인 매도']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2764,38 +2764,38 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3550</v>
+        <v>14130</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-8.15%</t>
+          <t>-5.55%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.39</v>
       </c>
       <c r="E26" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F26" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="G26" t="n">
-        <v>118</v>
+        <v>238</v>
       </c>
       <c r="H26" t="n">
-        <v>0.73</v>
+        <v>2.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>3865</v>
+        <v>14960</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2815,10 +2815,10 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.54</v>
+        <v>2.89</v>
       </c>
       <c r="O26" t="n">
-        <v>40509000000</v>
+        <v>53953000000</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2827,128 +2827,128 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>64000</v>
+        <v>-128000</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
+          <t>외국인 매수세 유입 및 기술적 상승 기대감. 높은 목표가 설정 및 신중론 혼재.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['폭락', '주주', '전망']</t>
+          <t>['외국인 매수', '기술적 상승', '목표가']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>232000</v>
+        <v>3575</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-8.30%</t>
+          <t>-7.50%</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-0.96</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>221</v>
+        <v>58</v>
       </c>
       <c r="F27" t="n">
-        <v>109</v>
+        <v>38</v>
       </c>
       <c r="G27" t="n">
-        <v>768</v>
+        <v>123</v>
       </c>
       <c r="H27" t="n">
-        <v>7.58</v>
+        <v>0.73</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>253000</v>
+        <v>3865</v>
       </c>
       <c r="K27" t="n">
-        <v>241000</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>241000</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>231000</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>8.539999999999999</v>
+        <v>1.54</v>
       </c>
       <c r="O27" t="n">
-        <v>170782942000</v>
+        <v>40874000000</v>
       </c>
       <c r="P27" t="n">
-        <v>426000</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>86100</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>-298000</v>
+        <v>64000</v>
       </c>
       <c r="S27" t="n">
-        <v>-18000</v>
+        <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>9월 TC본더 수출 데이터 관련 언급과 공매도 관련 내용이 있으나, 주가 방어 및 회사 차원의 소각/무증 발표 요구 등 감정적이고 구체적 근거가 부족한 내용이 혼재.</t>
+          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['TC본더', '공매도', '소각']</t>
+          <t>['폭락', '주주', '전망']</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>067290</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260911_12.xlsx
+++ b/data/trending_integrated_20260911_12.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15560</v>
+        <v>16060</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+28.70%</t>
+          <t>+27.36%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3.11</v>
+        <v>-0.22</v>
       </c>
       <c r="E2" t="n">
-        <v>358</v>
+        <v>131</v>
       </c>
       <c r="F2" t="n">
-        <v>216</v>
+        <v>90</v>
       </c>
       <c r="G2" t="n">
-        <v>864</v>
+        <v>131</v>
       </c>
       <c r="H2" t="n">
-        <v>3.14</v>
+        <v>2.39</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>12090</v>
+        <v>12610</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -607,10 +607,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03</v>
+        <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>185989000000</v>
+        <v>207443000000</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -619,14 +619,14 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-359000</v>
+        <v>-71000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>국제 유가 급등에 따른 급등세. 사우디, 중동 전쟁 관련 호재 및 외국인 대량 매수 유입.</t>
+          <t>젠슨 황의 AI 다음 시장으로 사이버 보안 지목에 따른 테마주 부각. 거래량 폭증 및 주가 급등.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,11 +635,11 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['국제 유가', '중동 전쟁', '외국인 매수']</t>
+          <t>['사이버보안', '젠슨황', 'AI']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16060</v>
+        <v>2550</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+27.36%</t>
+          <t>+20.00%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.22</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="F3" t="n">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H3" t="n">
-        <v>2.39</v>
+        <v>3.83</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>12610</v>
+        <v>2125</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2230</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2692</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2170</v>
       </c>
       <c r="N3" t="n">
-        <v>2.61</v>
+        <v>3.76</v>
       </c>
       <c r="O3" t="n">
-        <v>207402000000</v>
+        <v>94143053699</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4810</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="R3" t="n">
-        <v>-71000</v>
+        <v>-1884000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>AI 다음 시장으로 사이버 보안 주목. 젠슨 황 발언 및 관련 뉴스 인용, 양자보안 기술 강조.</t>
+          <t>양자컴퓨터 관련 정부 지원 및 모건스탠리 매집 공시를 통한 상승 기대감 형성. 거래량 증가.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['사이버보안', '젠슨황', '양자보안']</t>
+          <t>['양자컴퓨터', '공급계약', '모건스탠리']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,46 +740,46 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2565</v>
+        <v>136700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+20.14%</t>
+          <t>+17.54%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.26</v>
       </c>
       <c r="E4" t="n">
-        <v>86</v>
+        <v>131</v>
       </c>
       <c r="F4" t="n">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="G4" t="n">
-        <v>110</v>
+        <v>265</v>
       </c>
       <c r="H4" t="n">
-        <v>3.83</v>
+        <v>4.32</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2135</v>
+        <v>116300</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.76</v>
+        <v>4.58</v>
       </c>
       <c r="O4" t="n">
-        <v>93527000000</v>
+        <v>441760000000</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -803,14 +803,14 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-1884000</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>양자컴퓨터 및 사이버 보안 테마 관련 언급. 외국인 및 프로그램 매도 물량 출회.</t>
+          <t>매출 호조 및 애플 관련 호재 가능성 언급. 거래량 부족 및 단기 급등에 대한 경계심 혼재.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['양자컴퓨터', '사이버 보안', '외국인 매도']</t>
+          <t>['매출 호조', '애플', '거래량']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,77 +832,77 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>001820</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>137800</v>
+        <v>7660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+19.10%</t>
+          <t>+16.59%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.26</v>
+        <v>-0.79</v>
       </c>
       <c r="E5" t="n">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="F5" t="n">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="G5" t="n">
-        <v>257</v>
+        <v>303</v>
       </c>
       <c r="H5" t="n">
-        <v>4.32</v>
+        <v>2.15</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>115700</v>
+        <v>6570</v>
       </c>
       <c r="K5" t="n">
-        <v>112100</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>147500</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>112000</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.58</v>
+        <v>2.94</v>
       </c>
       <c r="O5" t="n">
-        <v>438909664100</v>
+        <v>149381000000</v>
       </c>
       <c r="P5" t="n">
-        <v>196800</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>27750</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>52000</v>
+        <v>141000</v>
       </c>
       <c r="S5" t="n">
-        <v>96000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>매출 호조 및 애플 관련 호재 가능성 언급. 거래량 부족 및 단기 급등에 대한 경계심 혼재.</t>
+          <t>통신 및 위성네트워크 사업 관련 기대감. 공매도 감소 언급 및 단기 급등 가능성 제시.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['매출 호조', '애플', '거래량']</t>
+          <t>['통신', '위성네트워크', '공매도']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,46 +924,46 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7690</v>
+        <v>1921</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+17.05%</t>
+          <t>+9.15%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.79</v>
+        <v>0.32</v>
       </c>
       <c r="E6" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="F6" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G6" t="n">
-        <v>300</v>
+        <v>181</v>
       </c>
       <c r="H6" t="n">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6570</v>
+        <v>1760</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -975,10 +975,10 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.94</v>
+        <v>2.12</v>
       </c>
       <c r="O6" t="n">
-        <v>148139000000</v>
+        <v>39932000000</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -987,14 +987,14 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>141000</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>통신 및 위성네트워크 사업 관련 기대감. 공매도 감소 언급 및 단기 급등 가능성 제시.</t>
+          <t>홍해 사태 관련 전쟁 테마주로 분류되며 유가 상승 기대감 존재. 장금상선과의 비교 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['통신', '위성네트워크', '공매도']</t>
+          <t>['전쟁테마주', '유가상승', '홍해사태']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,46 +1016,46 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8300</v>
+        <v>7680</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+11.86%</t>
+          <t>+8.17%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="E7" t="n">
-        <v>179</v>
+        <v>120</v>
       </c>
       <c r="F7" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
-        <v>804</v>
+        <v>386</v>
       </c>
       <c r="H7" t="n">
-        <v>1.29</v>
+        <v>11.72</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>7420</v>
+        <v>7100</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1067,7 +1067,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.17</v>
+        <v>11.62</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1079,27 +1079,27 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-12000</v>
+        <v>43000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>9월 14일 WCLC(세계폐암학회)에서의 센딥파텔 교수 데이터 발표에 따른 주가 대폭등 예고. 기술 수출 및 글로벌 빅파마와의 협력 기대.</t>
+          <t>금호타이어의 주가 상승 저해 요인 및 기관 매수세 가능성 언급. 삼전닉스의 부지 요구 관련 내용 포함. 공매도 단가 상승 및 주가 흐름에 대한 분석.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['WCLC', '폐암학회', '기술 수출']</t>
+          <t>['공매도', '기관매수', '주가흐름']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1921</v>
+        <v>15560</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+9.15%</t>
+          <t>+7.24%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.32</v>
+        <v>3.11</v>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>366</v>
       </c>
       <c r="F8" t="n">
-        <v>57</v>
+        <v>223</v>
       </c>
       <c r="G8" t="n">
-        <v>180</v>
+        <v>856</v>
       </c>
       <c r="H8" t="n">
-        <v>2.44</v>
+        <v>3.14</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1760</v>
+        <v>14510</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>17010</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>17310</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>15290</v>
       </c>
       <c r="N8" t="n">
-        <v>2.12</v>
+        <v>0.03</v>
       </c>
       <c r="O8" t="n">
-        <v>39793000000</v>
+        <v>188072639630</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>36200</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>8920</v>
       </c>
       <c r="R8" t="n">
-        <v>-591000</v>
+        <v>-359000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>이란 테마주 연계 급등 기대감 속 차익실현 매물 출현. 유가 상승 및 지정학적 리스크로 인한 수혜 전망.</t>
+          <t>국제 유가 급등에 따른 급등세. 사우디, 중동 전쟁 관련 호재 및 외국인 대량 매수 유입.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['전쟁테마주', '유가상승', '정유업계']</t>
+          <t>['국제 유가', '중동 전쟁', '외국인 매수']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9990</v>
+        <v>26600</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+7.65%</t>
+          <t>+1.92%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>68</v>
+        <v>272</v>
       </c>
       <c r="F9" t="n">
-        <v>40</v>
+        <v>131</v>
       </c>
       <c r="G9" t="n">
-        <v>302</v>
+        <v>447</v>
       </c>
       <c r="H9" t="n">
-        <v>4.49</v>
+        <v>0.32</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,143 +1239,143 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>9280</v>
+        <v>26100</v>
       </c>
       <c r="K9" t="n">
-        <v>10030</v>
+        <v>26350</v>
       </c>
       <c r="L9" t="n">
-        <v>10880</v>
+        <v>30300</v>
       </c>
       <c r="M9" t="n">
-        <v>9800</v>
+        <v>25400</v>
       </c>
       <c r="N9" t="n">
-        <v>4.42</v>
+        <v>0.33</v>
       </c>
       <c r="O9" t="n">
-        <v>20691356750</v>
+        <v>312688161825</v>
       </c>
       <c r="P9" t="n">
-        <v>15640</v>
+        <v>39350</v>
       </c>
       <c r="Q9" t="n">
-        <v>5470</v>
+        <v>8200</v>
       </c>
       <c r="R9" t="n">
-        <v>-88000</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
+          <t>타 급등주 대비 상대적 선방 및 외인 유입 기대감 형성. 시장 하락장 속 방어적 흐름.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
+          <t>['급등주', '외국인유입', '하락장']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26650</v>
+        <v>253000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+2.11%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.01</v>
+        <v>-0.96</v>
       </c>
       <c r="E10" t="n">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="F10" t="n">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="G10" t="n">
-        <v>443</v>
+        <v>818</v>
       </c>
       <c r="H10" t="n">
-        <v>0.32</v>
+        <v>7.58</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>26100</v>
+        <v>250500</v>
       </c>
       <c r="K10" t="n">
-        <v>26350</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>30300</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>25400</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.33</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>311060225850</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>39350</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>8200</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>7000</v>
+        <v>-298000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-18000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>타 급등주 대비 상대적 선방 및 외인 유입 기대감 형성. 시장 하락장 속 방어적 흐름.</t>
+          <t>반도체 수출 호조에도 불구하고 공매도 세력의 압박과 주가 하락에 대한 불만 표출. 기관 매수세 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['급등주', '외국인유입', '하락장']</t>
+          <t>['반도체수출', '공매도', '기관매수']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>253000</v>
+        <v>53100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.96</v>
+        <v>-0.44</v>
       </c>
       <c r="E11" t="n">
-        <v>223</v>
+        <v>68</v>
       </c>
       <c r="F11" t="n">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="G11" t="n">
-        <v>787</v>
+        <v>131</v>
       </c>
       <c r="H11" t="n">
-        <v>7.58</v>
+        <v>2.92</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>250500</v>
+        <v>53200</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1435,10 +1435,10 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>8.539999999999999</v>
+        <v>3.36</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>90309000000</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1447,23 +1447,23 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-298000</v>
+        <v>116000</v>
       </c>
       <c r="S11" t="n">
-        <v>-18000</v>
+        <v>10000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>9월 TC 본더 수출 데이터 및 반도체 수출 증가 뉴스 언급. 기관 매수세 확인 및 공매도 청산 요구.</t>
+          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['TC본더', '공매도', '수출 데이터']</t>
+          <t>['태양광', '고유가', '신호가']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1471,43 +1471,43 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>475150</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>90000</v>
+        <v>50300</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.06</v>
+        <v>0.09</v>
       </c>
       <c r="E12" t="n">
-        <v>206</v>
+        <v>146</v>
       </c>
       <c r="F12" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="G12" t="n">
-        <v>803</v>
+        <v>553</v>
       </c>
       <c r="H12" t="n">
-        <v>23.59</v>
+        <v>38.78</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>89900</v>
+        <v>50400</v>
       </c>
       <c r="K12" t="n">
-        <v>88700</v>
+        <v>50500</v>
       </c>
       <c r="L12" t="n">
-        <v>91000</v>
+        <v>51200</v>
       </c>
       <c r="M12" t="n">
-        <v>88000</v>
+        <v>49650</v>
       </c>
       <c r="N12" t="n">
-        <v>23.65</v>
+        <v>38.69</v>
       </c>
       <c r="O12" t="n">
-        <v>132594758500</v>
+        <v>58320349575</v>
       </c>
       <c r="P12" t="n">
-        <v>139200</v>
+        <v>67300</v>
       </c>
       <c r="Q12" t="n">
-        <v>57000</v>
+        <v>23150</v>
       </c>
       <c r="R12" t="n">
-        <v>-264000</v>
+        <v>-134000</v>
       </c>
       <c r="S12" t="n">
-        <v>26000</v>
+        <v>2000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 투자 협상 마무리 및 중동 에너지 공급망 이슈에 따른 두산에너빌리티의 수혜 기대. 수주 잔고 언급.</t>
+          <t>약 4.7조원 규모의 대규모 수주 공시로 인한 긍정적 시장 반응 및 상승 추세 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['원전', '에너지 공급망', '수주 잔고']</t>
+          <t>['수주', '공시', '추세']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>415000</v>
+        <v>415500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.2</v>
       </c>
       <c r="E13" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F13" t="n">
         <v>46</v>
       </c>
       <c r="G13" t="n">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H13" t="n">
         <v>38.02</v>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>415500</v>
+        <v>417500</v>
       </c>
       <c r="K13" t="n">
-        <v>407000</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>418000</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>404000</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>37.82</v>
       </c>
       <c r="O13" t="n">
-        <v>47169884250</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>822000</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>283000</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미래차 및 로봇 신기술 공개 및 수주 소식. 그룹사 양산 로드맵 가동 및 대차상환 후 순매수 유입.</t>
+          <t>로봇 부품 수주 등 미래차 및 로봇 사업 확장 관련 긍정적 뉴스. 대차 상환 및 외국인 매수세 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['미래차', '로봇 신기술', '수주']</t>
+          <t>['로봇', '수주', '미래차']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1853000</v>
+        <v>29550</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.12</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>52</v>
       </c>
       <c r="F14" t="n">
-        <v>448</v>
+        <v>40</v>
       </c>
       <c r="G14" t="n">
-        <v>1493</v>
+        <v>144</v>
       </c>
       <c r="H14" t="n">
-        <v>50.55</v>
+        <v>25.55</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1856000</v>
+        <v>29800</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1711,7 +1711,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>50.67</v>
+        <v>24.99</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1723,67 +1723,67 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-249000</v>
+        <v>265000</v>
       </c>
       <c r="S14" t="n">
-        <v>-102000</v>
+        <v>-69000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국장 대비 선방 중이나, 향후 하이닉스의 영업이익 전망에 대한 부정적 의견 존재. 개인 투자자 매수세 및 유가, 금리 변동성 언급.</t>
+          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['영업이익', '개인투자자', '금리']</t>
+          <t>['유럽 자금', '환율', '유가']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52800</v>
+        <v>19580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-0.86%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.44</v>
+        <v>0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>68</v>
+        <v>129</v>
       </c>
       <c r="F15" t="n">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="G15" t="n">
-        <v>131</v>
+        <v>462</v>
       </c>
       <c r="H15" t="n">
-        <v>2.92</v>
+        <v>10.65</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,99 +1791,99 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>53200</v>
+        <v>19750</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>19500</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>19840</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>19060</v>
       </c>
       <c r="N15" t="n">
-        <v>3.36</v>
+        <v>10.64</v>
       </c>
       <c r="O15" t="n">
-        <v>89412000000</v>
+        <v>90519306785</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>40350</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3320</v>
       </c>
       <c r="R15" t="n">
-        <v>116000</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
+          <t>대차 해지 독려를 통한 공매도 세력에 대한 주주들의 저항 의지 표출. 원전 투자 등 호재 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['태양광', '고유가', '신호가']</t>
+          <t>['대차해지', '공매도', '원전투자']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>50400</v>
+        <v>14130</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.09</v>
+        <v>-0.11</v>
       </c>
       <c r="E16" t="n">
-        <v>142</v>
+        <v>93</v>
       </c>
       <c r="F16" t="n">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="G16" t="n">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="H16" t="n">
-        <v>38.78</v>
+        <v>5.98</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>50800</v>
+        <v>14320</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1895,10 +1895,10 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>38.69</v>
+        <v>6.09</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>91917000000</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1907,27 +1907,27 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-134000</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>약 4.7조원 규모의 대규모 수주 공시로 인한 긍정적 시장 반응 및 상승 추세 기대.</t>
+          <t>원전 관련 섹터 상승 기대감 및 공매도 세력과의 갈등 양상. 모건 증권의 대량 매도 물량 출회.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['수주', '공시', '추세']</t>
+          <t>['원전', '공매도', '모건 증권']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,138 +1936,138 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19570</v>
+        <v>3560</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-1.66%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.01</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="F17" t="n">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="G17" t="n">
-        <v>459</v>
+        <v>126</v>
       </c>
       <c r="H17" t="n">
-        <v>10.65</v>
+        <v>0.73</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>19750</v>
+        <v>3620</v>
       </c>
       <c r="K17" t="n">
-        <v>19500</v>
+        <v>3725</v>
       </c>
       <c r="L17" t="n">
-        <v>19840</v>
+        <v>3915</v>
       </c>
       <c r="M17" t="n">
-        <v>19060</v>
+        <v>3520</v>
       </c>
       <c r="N17" t="n">
-        <v>10.64</v>
+        <v>1.54</v>
       </c>
       <c r="O17" t="n">
-        <v>87873388835</v>
+        <v>41018515312</v>
       </c>
       <c r="P17" t="n">
-        <v>40350</v>
+        <v>4335</v>
       </c>
       <c r="Q17" t="n">
-        <v>3320</v>
+        <v>1246</v>
       </c>
       <c r="R17" t="n">
-        <v>-233000</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-16000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>대차해지 독려 및 목표가 상향 뉴스 언급. 공매도 세력과의 대립 구도 형성.</t>
+          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['대차해지', '목표가 상향', '공매도']</t>
+          <t>['폭락', '주주', '전망']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14130</v>
+        <v>8800</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-1.68%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.11</v>
+        <v>0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F18" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G18" t="n">
-        <v>548</v>
+        <v>249</v>
       </c>
       <c r="H18" t="n">
-        <v>5.98</v>
+        <v>27.19</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>14320</v>
+        <v>8950</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2079,10 +2079,10 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>6.09</v>
+        <v>27.16</v>
       </c>
       <c r="O18" t="n">
-        <v>90412000000</v>
+        <v>15656000000</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -2091,27 +2091,27 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-371000</v>
+        <v>-100000</v>
       </c>
       <c r="S18" t="n">
-        <v>-69000</v>
+        <v>-78000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>원전 관련 섹터 상승 기대감 및 공매도 세력과의 갈등 양상. 모건 증권의 대량 매도 물량 출회.</t>
+          <t>회사의 경영 실적 악화 및 주가 부진에 대한 불만 고조. 기술적 반등 기대감도 낮음.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['원전', '공매도', '모건 증권']</t>
+          <t>['경영 실적', '주가 부진', '기술적 반등']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8800</v>
+        <v>89900</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.68%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="F19" t="n">
-        <v>51</v>
+        <v>121</v>
       </c>
       <c r="G19" t="n">
-        <v>249</v>
+        <v>814</v>
       </c>
       <c r="H19" t="n">
-        <v>27.19</v>
+        <v>23.59</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>8950</v>
+        <v>91700</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2171,10 +2171,10 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>27.16</v>
+        <v>23.65</v>
       </c>
       <c r="O19" t="n">
-        <v>15409000000</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -2190,20 +2190,20 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>회사의 경영 실적 악화 및 주가 부진에 대한 불만 고조. 기술적 반등 기대감도 낮음.</t>
+          <t>미국 투자 협상 마무리 및 중동 에너지 공급망 이슈에 따른 두산에너빌리티의 수혜 기대. 수주 잔고 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['경영 실적', '주가 부진', '기술적 반등']</t>
+          <t>['원전', '에너지 공급망', '수주 잔고']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -2223,18 +2223,18 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14720</v>
+        <v>15040</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.13%</t>
+          <t>-3.84%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F20" t="n">
         <v>40</v>
@@ -2251,28 +2251,28 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>15040</v>
+        <v>15640</v>
       </c>
       <c r="K20" t="n">
-        <v>14550</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>15260</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>14350</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>18496884070</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>19380</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>22000</v>
@@ -2311,83 +2311,83 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>192900</v>
+        <v>14160</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.33%</t>
+          <t>-3.93%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.39</v>
       </c>
       <c r="E21" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="F21" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G21" t="n">
-        <v>134</v>
+        <v>251</v>
       </c>
       <c r="H21" t="n">
-        <v>75.98999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>197500</v>
+        <v>14740</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>14050</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>14560</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>14030</v>
       </c>
       <c r="N21" t="n">
-        <v>75.92</v>
+        <v>2.89</v>
       </c>
       <c r="O21" t="n">
-        <v>395413000000</v>
+        <v>54933716610</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1272</v>
       </c>
       <c r="R21" t="n">
-        <v>-852000</v>
+        <v>-128000</v>
       </c>
       <c r="S21" t="n">
-        <v>-123000</v>
+        <v>-6000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>연속적인 하락세와 외국인/기관 매도세 지속. 특별 배당 기대감 있으나 주가 흐름은 부정적.</t>
+          <t>외국인 매수세 유입 및 기술적 상승 기대감. 높은 목표가 설정 및 신중론 혼재.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['주가 하락', '외국인 매도', '특별 배당']</t>
+          <t>['외국인 매수', '기술적 상승', '목표가']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>28650</v>
+        <v>1778000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.05%</t>
+          <t>-4.05%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="E22" t="n">
-        <v>51</v>
+        <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>39</v>
+        <v>448</v>
       </c>
       <c r="G22" t="n">
-        <v>140</v>
+        <v>1552</v>
       </c>
       <c r="H22" t="n">
-        <v>51.34</v>
+        <v>50.55</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,183 +2435,183 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>29550</v>
+        <v>1853000</v>
       </c>
       <c r="K22" t="n">
-        <v>28650</v>
+        <v>1773000</v>
       </c>
       <c r="L22" t="n">
-        <v>28900</v>
+        <v>1795000</v>
       </c>
       <c r="M22" t="n">
-        <v>28500</v>
+        <v>1768000</v>
       </c>
       <c r="N22" t="n">
-        <v>24.99</v>
+        <v>50.67</v>
       </c>
       <c r="O22" t="n">
-        <v>39929414450</v>
+        <v>2838734237000</v>
       </c>
       <c r="P22" t="n">
-        <v>31200</v>
+        <v>2987000</v>
       </c>
       <c r="Q22" t="n">
-        <v>21000</v>
+        <v>305500</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>-249000</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>-102000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
+          <t>개인 투자자의 매수세와 함께 박스권 돌파에 대한 기대감 및 불안감이 혼재. 자사주 매입 효과 언급.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['유럽 자금', '환율', '유가']</t>
+          <t>['박스권', '자사주매입', '개인투자자']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12610</v>
+        <v>257500</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.22%</t>
+          <t>-4.28%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.8</v>
+        <v>-0.1</v>
       </c>
       <c r="E23" t="n">
-        <v>75</v>
+        <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>44</v>
+        <v>506</v>
       </c>
       <c r="G23" t="n">
-        <v>85</v>
+        <v>1694</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9399999999999999</v>
+        <v>46.71</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>13030</v>
+        <v>269000</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>258000</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>261000</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>256500</v>
       </c>
       <c r="N23" t="n">
-        <v>0.14</v>
+        <v>46.81</v>
       </c>
       <c r="O23" t="n">
-        <v>54692000000</v>
+        <v>2270955225500</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>374500</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>72100</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>-1232000</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>-646000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>원전 테마주로서의 삼미금속 언급. 한전기술 등 타 원전주들의 급등 속 상대적 부진 및 거래량 부족에 대한 지적.</t>
+          <t>증권사 리포트 및 국내외 거시 경제 요인에 대한 부정적 언급과 함께 주가 하락에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['원전', '테마주', '거래량']</t>
+          <t>['골드만삭스', '반도체', '주가하락']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>5</v>
+        <v>104</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7380</v>
+        <v>192900</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-3.91%</t>
+          <t>-4.98%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="F24" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G24" t="n">
-        <v>379</v>
+        <v>145</v>
       </c>
       <c r="H24" t="n">
-        <v>11.72</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2619,51 +2619,51 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>7680</v>
+        <v>203000</v>
       </c>
       <c r="K24" t="n">
-        <v>7540</v>
+        <v>195000</v>
       </c>
       <c r="L24" t="n">
-        <v>7660</v>
+        <v>195600</v>
       </c>
       <c r="M24" t="n">
-        <v>7360</v>
+        <v>191000</v>
       </c>
       <c r="N24" t="n">
-        <v>11.62</v>
+        <v>75.92</v>
       </c>
       <c r="O24" t="n">
-        <v>8992359485</v>
+        <v>404958299600</v>
       </c>
       <c r="P24" t="n">
-        <v>8850</v>
+        <v>243500</v>
       </c>
       <c r="Q24" t="n">
-        <v>4220</v>
+        <v>58600</v>
       </c>
       <c r="R24" t="n">
-        <v>43000</v>
+        <v>-852000</v>
       </c>
       <c r="S24" t="n">
-        <v>-2000</v>
+        <v>-123000</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>금호타이어의 주가 상승 저해 요인 및 기관 매수세 가능성 언급. 삼전닉스의 부지 요구 관련 내용 포함. 공매도 단가 상승 및 주가 흐름에 대한 분석.</t>
+          <t>대형 증권사들의 매도세와 주가 하락에 대한 불만, 배당금 관련 논의.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['공매도', '기관매수', '주가흐름']</t>
+          <t>['우선주', '매도세', '배당금']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,46 +2672,46 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>258000</v>
+        <v>9280</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-4.27%</t>
+          <t>-5.31%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>800</v>
+        <v>68</v>
       </c>
       <c r="F25" t="n">
-        <v>509</v>
+        <v>40</v>
       </c>
       <c r="G25" t="n">
-        <v>1671</v>
+        <v>306</v>
       </c>
       <c r="H25" t="n">
-        <v>46.71</v>
+        <v>4.49</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>269500</v>
+        <v>9800</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -2723,10 +2723,10 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>46.81</v>
+        <v>4.42</v>
       </c>
       <c r="O25" t="n">
-        <v>2202792000000</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2735,67 +2735,67 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>-1232000</v>
+        <v>-88000</v>
       </c>
       <c r="S25" t="n">
-        <v>-646000</v>
+        <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>반도체 수출 최대치 기록에도 주가 하락세. 외국인 대량 매도 및 부정적 리포트 존재.</t>
+          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['반도체 수출', '주가 하락', '외국인 매도']</t>
+          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>104</v>
+        <v>2</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>064550</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>14130</v>
+        <v>12210</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-5.55%</t>
+          <t>-6.29%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-0.39</v>
+        <v>0.8</v>
       </c>
       <c r="E26" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="F26" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G26" t="n">
-        <v>238</v>
+        <v>89</v>
       </c>
       <c r="H26" t="n">
-        <v>2.5</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>14960</v>
+        <v>13030</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2815,10 +2815,10 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.89</v>
+        <v>0.14</v>
       </c>
       <c r="O26" t="n">
-        <v>53953000000</v>
+        <v>58136000000</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2827,27 +2827,27 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>-128000</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>외국인 매수세 유입 및 기술적 상승 기대감. 높은 목표가 설정 및 신중론 혼재.</t>
+          <t>원전 테마 및 타 종목과의 비교 언급 속에서 뚜렷한 호재 없이 계단식 하락 추세에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['외국인 매수', '기술적 상승', '목표가']</t>
+          <t>['가스터빈', '원전', '거래량']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2856,38 +2856,38 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3575</v>
+        <v>7750</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-7.50%</t>
+          <t>-6.63%</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="E27" t="n">
-        <v>58</v>
+        <v>184</v>
       </c>
       <c r="F27" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="G27" t="n">
-        <v>123</v>
+        <v>814</v>
       </c>
       <c r="H27" t="n">
-        <v>0.73</v>
+        <v>1.29</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2895,60 +2895,60 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>3865</v>
+        <v>8300</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>8400</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>8700</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>7540</v>
       </c>
       <c r="N27" t="n">
-        <v>1.54</v>
+        <v>1.17</v>
       </c>
       <c r="O27" t="n">
-        <v>40874000000</v>
+        <v>17225336285</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>21500</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="R27" t="n">
-        <v>64000</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
+          <t>9월 14일 WCLC(세계폐암학회)에서의 센딥파텔 교수 데이터 발표에 따른 주가 대폭등 예고. 기술 수출 및 글로벌 빅파마와의 협력 기대.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['폭락', '주주', '전망']</t>
+          <t>['WCLC', '폐암학회', '기술 수출']</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
